--- a/trial_source/document/エビデンス_Task25_画面レイアウト設計_勤怠管理画面(打鍵Ver).xlsx
+++ b/trial_source/document/エビデンス_Task25_画面レイアウト設計_勤怠管理画面(打鍵Ver).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abukawa\project\リアプロ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8163B2C-957C-4706-9D7C-F814B3D0DEEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3CC099-CE72-4705-AE4C-1A32C17CD8DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" tabRatio="602" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" tabRatio="602" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テストエビデンス作成観点" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'イベント処理1、8'!$A$1:$P$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'イベント処理1~10 (2)'!$A$1:$P$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'画面詳細（画面イメージ）'!$A$1:$V$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'画面詳細（画面イメージ）'!$A$1:$V$86</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'画面詳細（画面表示項目）'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="122">
   <si>
     <t>LMS学習管理システム</t>
   </si>
@@ -75,9 +75,6 @@
     <t>更新日</t>
   </si>
   <si>
-    <t>上村</t>
-  </si>
-  <si>
     <t>バージョン</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
   </si>
   <si>
     <t>新規作成</t>
-  </si>
-  <si>
-    <t>No.1</t>
   </si>
   <si>
     <t>（画面mock）</t>
@@ -435,16 +429,9 @@
     <phoneticPr fontId="32"/>
   </si>
   <si>
-    <t>画面詳細
-イベント処理</t>
+    <t>虻川</t>
     <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ショリ</t>
+      <t>アブカワ</t>
     </rPh>
     <phoneticPr fontId="32"/>
   </si>
@@ -453,6 +440,22 @@
     <rPh sb="0" eb="2">
       <t>アブカワ</t>
     </rPh>
+    <phoneticPr fontId="32"/>
+  </si>
+  <si>
+    <t>No27</t>
+    <phoneticPr fontId="32"/>
+  </si>
+  <si>
+    <t>No.1</t>
+    <phoneticPr fontId="32"/>
+  </si>
+  <si>
+    <t>No.2</t>
+    <phoneticPr fontId="32"/>
+  </si>
+  <si>
+    <t>No.3</t>
     <phoneticPr fontId="32"/>
   </si>
 </sst>
@@ -1116,7 +1119,7 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1225,29 +1228,29 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="19" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="19" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="19" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="19" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="19" fillId="9" borderId="0" xfId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1258,29 +1261,11 @@
     <xf numFmtId="178" fontId="19" fillId="9" borderId="10" xfId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="19" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="19" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="19" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="17" fillId="0" borderId="18" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="18" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="19" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1300,9 +1285,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="10" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1315,11 +1297,29 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="13" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="0" borderId="18" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="0" borderId="18" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="19" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="21">
@@ -1596,13 +1596,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>449640</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>203400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>132480</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>221400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1620,63 +1620,6 @@
         <a:xfrm>
           <a:off x="9722520" y="6147000"/>
           <a:ext cx="333000" cy="246600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28440">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>481680</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>171720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>345240</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="CustomShape 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="481680" y="2457720"/>
-          <a:ext cx="683280" cy="237960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1841,58 +1784,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>17319</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>549718</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>51954</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{352E5EDE-4A2F-4987-8EFC-FDC7D6731328}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="432955"/>
-          <a:ext cx="7130626" cy="3671454"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>22514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>579293</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>69273</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1909,7 +1808,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1930,14 +1829,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>142009</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>55419</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>569314</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>113433</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>26843</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1953,14 +1852,14 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="11087100"/>
+          <a:off x="0" y="10654146"/>
           <a:ext cx="7860269" cy="6032788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1972,60 +1871,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>51954</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>69274</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>34637</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>155863</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>97201</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69233528-1174-4594-8B76-1291ECFC4A1D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17283545" y="2216729"/>
-          <a:ext cx="6494318" cy="4773108"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>103876</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>106870</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>207819</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>34637</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2040,60 +1895,15 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect l="47511" t="8656" r="16074" b="31412"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17941636" y="8104909"/>
-          <a:ext cx="12174649" cy="2600688"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>32095</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>84372</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3B976F3-30D3-4D80-A419-913C1289C94A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17941636" y="12088091"/>
-          <a:ext cx="12812913" cy="8916644"/>
+          <a:off x="8035637" y="450272"/>
+          <a:ext cx="4433455" cy="1558638"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2106,13 +1916,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>710044</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>-1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>475633</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>69273</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2129,7 +1939,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2148,103 +1958,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>303929</xdr:colOff>
-      <xdr:row>177</xdr:row>
-      <xdr:rowOff>160582</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4CF8EA8-7983-4B38-8CBE-6FD86A845CCC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10841182" y="21959455"/>
-          <a:ext cx="12374702" cy="8992855"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>277091</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>14909</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5D5E01-EB98-4528-8F17-E34BDA9AF449}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8711045" y="415636"/>
-          <a:ext cx="5247409" cy="3651728"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>692727</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>34637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>508097</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>34637</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2261,7 +1983,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2274,6 +1996,51 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>517680</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>50553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D9F7220-5968-4C7C-8083-454882499072}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="484909"/>
+          <a:ext cx="5678498" cy="1539917"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -8673,2186 +8440,2195 @@
   <sheetData>
     <row r="2" spans="2:36" ht="18" x14ac:dyDescent="0.15">
       <c r="B2" s="37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.15">
+      <c r="B5" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="41"/>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="41"/>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B5" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="42"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="42"/>
-      <c r="AE5" s="42"/>
-      <c r="AF5" s="42"/>
-      <c r="AG5" s="42"/>
-      <c r="AH5" s="42"/>
-      <c r="AI5" s="42"/>
-      <c r="AJ5" s="42"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="39"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="39"/>
+      <c r="AA5" s="39"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B6" s="38">
+      <c r="B6" s="40">
         <f>ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B7" s="38">
+      <c r="B7" s="40">
         <f t="shared" ref="B7:B15" si="0">ROW()-4</f>
         <v>3</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="42"/>
+      <c r="AB7" s="42"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="42"/>
+      <c r="AF7" s="42"/>
+      <c r="AG7" s="42"/>
+      <c r="AH7" s="42"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="42"/>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B8" s="38">
+      <c r="B8" s="40">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="39"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="39"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="39"/>
-      <c r="AF8" s="39"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="39"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="42"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="42"/>
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="42"/>
+      <c r="AD8" s="42"/>
+      <c r="AE8" s="42"/>
+      <c r="AF8" s="42"/>
+      <c r="AG8" s="42"/>
+      <c r="AH8" s="42"/>
+      <c r="AI8" s="42"/>
+      <c r="AJ8" s="42"/>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B9" s="38">
+      <c r="B9" s="40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="39"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="42"/>
+      <c r="Z9" s="42"/>
+      <c r="AA9" s="42"/>
+      <c r="AB9" s="42"/>
+      <c r="AC9" s="42"/>
+      <c r="AD9" s="42"/>
+      <c r="AE9" s="42"/>
+      <c r="AF9" s="42"/>
+      <c r="AG9" s="42"/>
+      <c r="AH9" s="42"/>
+      <c r="AI9" s="42"/>
+      <c r="AJ9" s="42"/>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B10" s="38">
+      <c r="B10" s="40">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="39"/>
-      <c r="W10" s="39"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="39"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="39"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="39"/>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="39"/>
-      <c r="AI10" s="39"/>
-      <c r="AJ10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="42"/>
+      <c r="Y10" s="42"/>
+      <c r="Z10" s="42"/>
+      <c r="AA10" s="42"/>
+      <c r="AB10" s="42"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="42"/>
+      <c r="AE10" s="42"/>
+      <c r="AF10" s="42"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="42"/>
+      <c r="AI10" s="42"/>
+      <c r="AJ10" s="42"/>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B11" s="38">
+      <c r="B11" s="40">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="42"/>
+      <c r="AA11" s="42"/>
+      <c r="AB11" s="42"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="42"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="42"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="42"/>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B12" s="38">
+      <c r="B12" s="40">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="42"/>
+      <c r="AA12" s="42"/>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="42"/>
+      <c r="AE12" s="42"/>
+      <c r="AF12" s="42"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="42"/>
+      <c r="AI12" s="42"/>
+      <c r="AJ12" s="42"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B13" s="38">
+      <c r="B13" s="40">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="39"/>
-      <c r="AI13" s="39"/>
-      <c r="AJ13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="42"/>
+      <c r="AA13" s="42"/>
+      <c r="AB13" s="42"/>
+      <c r="AC13" s="42"/>
+      <c r="AD13" s="42"/>
+      <c r="AE13" s="42"/>
+      <c r="AF13" s="42"/>
+      <c r="AG13" s="42"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="42"/>
+      <c r="AJ13" s="42"/>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B14" s="38">
+      <c r="B14" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="39"/>
-      <c r="AA14" s="39"/>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="39"/>
-      <c r="AE14" s="39"/>
-      <c r="AF14" s="39"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="39"/>
-      <c r="AI14" s="39"/>
-      <c r="AJ14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="42"/>
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
+      <c r="AH14" s="42"/>
+      <c r="AI14" s="42"/>
+      <c r="AJ14" s="42"/>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B15" s="38">
+      <c r="B15" s="40">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="42"/>
+      <c r="W15" s="42"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="42"/>
+      <c r="AG15" s="42"/>
+      <c r="AH15" s="42"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="42"/>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B16" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="41"/>
+      <c r="B16" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
+      <c r="AA16" s="38"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="38"/>
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="38"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="38"/>
+      <c r="AI16" s="38"/>
+      <c r="AJ16" s="38"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B17" s="38">
+      <c r="B17" s="40">
         <v>1</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="39"/>
-      <c r="T17" s="39"/>
-      <c r="U17" s="39"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="39"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="39"/>
-      <c r="Z17" s="39"/>
-      <c r="AA17" s="39"/>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="39"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="39"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="39"/>
-      <c r="AH17" s="39"/>
-      <c r="AI17" s="39"/>
-      <c r="AJ17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="42"/>
     </row>
     <row r="18" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B18" s="38">
+      <c r="B18" s="40">
         <f>B17+1</f>
         <v>2</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="39"/>
-      <c r="W18" s="39"/>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="39"/>
-      <c r="Z18" s="39"/>
-      <c r="AA18" s="39"/>
-      <c r="AB18" s="39"/>
-      <c r="AC18" s="39"/>
-      <c r="AD18" s="39"/>
-      <c r="AE18" s="39"/>
-      <c r="AF18" s="39"/>
-      <c r="AG18" s="39"/>
-      <c r="AH18" s="39"/>
-      <c r="AI18" s="39"/>
-      <c r="AJ18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="42"/>
     </row>
     <row r="19" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B19" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="41"/>
-      <c r="AE19" s="41"/>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="41"/>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="41"/>
+      <c r="B19" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="38"/>
+      <c r="AJ19" s="38"/>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B20" s="38">
+      <c r="B20" s="40">
         <v>1</v>
       </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="39"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="39"/>
-      <c r="AA20" s="39"/>
-      <c r="AB20" s="39"/>
-      <c r="AC20" s="39"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="39"/>
-      <c r="AF20" s="39"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="42"/>
     </row>
     <row r="21" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B21" s="38">
+      <c r="B21" s="40">
         <f>B20+1</f>
         <v>2</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="39"/>
-      <c r="U21" s="39"/>
-      <c r="V21" s="39"/>
-      <c r="W21" s="39"/>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="39"/>
-      <c r="Z21" s="39"/>
-      <c r="AA21" s="39"/>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="39"/>
-      <c r="AE21" s="39"/>
-      <c r="AF21" s="39"/>
-      <c r="AG21" s="39"/>
-      <c r="AH21" s="39"/>
-      <c r="AI21" s="39"/>
-      <c r="AJ21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="42"/>
+      <c r="AC21" s="42"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="42"/>
+      <c r="AG21" s="42"/>
+      <c r="AH21" s="42"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="42"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B22" s="38">
+      <c r="B22" s="40">
         <f>B21+1</f>
         <v>3</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="39"/>
-      <c r="W22" s="39"/>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
-      <c r="AA22" s="39"/>
-      <c r="AB22" s="39"/>
-      <c r="AC22" s="39"/>
-      <c r="AD22" s="39"/>
-      <c r="AE22" s="39"/>
-      <c r="AF22" s="39"/>
-      <c r="AG22" s="39"/>
-      <c r="AH22" s="39"/>
-      <c r="AI22" s="39"/>
-      <c r="AJ22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42"/>
+      <c r="X22" s="42"/>
+      <c r="Y22" s="42"/>
+      <c r="Z22" s="42"/>
+      <c r="AA22" s="42"/>
+      <c r="AB22" s="42"/>
+      <c r="AC22" s="42"/>
+      <c r="AD22" s="42"/>
+      <c r="AE22" s="42"/>
+      <c r="AF22" s="42"/>
+      <c r="AG22" s="42"/>
+      <c r="AH22" s="42"/>
+      <c r="AI22" s="42"/>
+      <c r="AJ22" s="42"/>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B23" s="38">
+      <c r="B23" s="40">
         <f>B22+1</f>
         <v>4</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="39"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="39"/>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="39"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="39"/>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="39"/>
-      <c r="AH23" s="39"/>
-      <c r="AI23" s="39"/>
-      <c r="AJ23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="42"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="42"/>
+      <c r="AC23" s="42"/>
+      <c r="AD23" s="42"/>
+      <c r="AE23" s="42"/>
+      <c r="AF23" s="42"/>
+      <c r="AG23" s="42"/>
+      <c r="AH23" s="42"/>
+      <c r="AI23" s="42"/>
+      <c r="AJ23" s="42"/>
     </row>
     <row r="24" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B24" s="38">
+      <c r="B24" s="40">
         <f>B23+1</f>
         <v>5</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="39"/>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="39"/>
-      <c r="AH24" s="39"/>
-      <c r="AI24" s="39"/>
-      <c r="AJ24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="42"/>
+      <c r="Z24" s="42"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="42"/>
+      <c r="AC24" s="42"/>
+      <c r="AD24" s="42"/>
+      <c r="AE24" s="42"/>
+      <c r="AF24" s="42"/>
+      <c r="AG24" s="42"/>
+      <c r="AH24" s="42"/>
+      <c r="AI24" s="42"/>
+      <c r="AJ24" s="42"/>
     </row>
     <row r="25" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B25" s="38">
+      <c r="B25" s="40">
         <f>B24+1</f>
         <v>6</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
-      <c r="T25" s="39"/>
-      <c r="U25" s="39"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="39"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="39"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="39"/>
-      <c r="AI25" s="39"/>
-      <c r="AJ25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="42"/>
+      <c r="W25" s="42"/>
+      <c r="X25" s="42"/>
+      <c r="Y25" s="42"/>
+      <c r="Z25" s="42"/>
+      <c r="AA25" s="42"/>
+      <c r="AB25" s="42"/>
+      <c r="AC25" s="42"/>
+      <c r="AD25" s="42"/>
+      <c r="AE25" s="42"/>
+      <c r="AF25" s="42"/>
+      <c r="AG25" s="42"/>
+      <c r="AH25" s="42"/>
+      <c r="AI25" s="42"/>
+      <c r="AJ25" s="42"/>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B26" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="41"/>
-      <c r="Z26" s="41"/>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="41"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="41"/>
+      <c r="B26" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AE26" s="38"/>
+      <c r="AF26" s="38"/>
+      <c r="AG26" s="38"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="38"/>
     </row>
     <row r="27" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B27" s="38">
+      <c r="B27" s="40">
         <v>1</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="40"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="40"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="40"/>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="40"/>
-      <c r="AG27" s="40"/>
-      <c r="AH27" s="40"/>
-      <c r="AI27" s="40"/>
-      <c r="AJ27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B28" s="38">
+      <c r="B28" s="40">
         <f>B27+1</f>
         <v>2</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="39"/>
-      <c r="W28" s="39"/>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="39"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="39"/>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="39"/>
-      <c r="AE28" s="39"/>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="39"/>
-      <c r="AI28" s="39"/>
-      <c r="AJ28" s="39"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="42"/>
+      <c r="W28" s="42"/>
+      <c r="X28" s="42"/>
+      <c r="Y28" s="42"/>
+      <c r="Z28" s="42"/>
+      <c r="AA28" s="42"/>
+      <c r="AB28" s="42"/>
+      <c r="AC28" s="42"/>
+      <c r="AD28" s="42"/>
+      <c r="AE28" s="42"/>
+      <c r="AF28" s="42"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
     </row>
     <row r="29" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B29" s="38">
+      <c r="B29" s="40">
         <f>B28+1</f>
         <v>3</v>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="39"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="39"/>
-      <c r="W29" s="39"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="39"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="39"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="39"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="39"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="39"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="42"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="42"/>
+      <c r="W29" s="42"/>
+      <c r="X29" s="42"/>
+      <c r="Y29" s="42"/>
+      <c r="Z29" s="42"/>
+      <c r="AA29" s="42"/>
+      <c r="AB29" s="42"/>
+      <c r="AC29" s="42"/>
+      <c r="AD29" s="42"/>
+      <c r="AE29" s="42"/>
+      <c r="AF29" s="42"/>
+      <c r="AG29" s="42"/>
+      <c r="AH29" s="42"/>
+      <c r="AI29" s="42"/>
+      <c r="AJ29" s="42"/>
     </row>
     <row r="30" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B30" s="38">
+      <c r="B30" s="40">
         <f>B29+1</f>
         <v>4</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="39"/>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="39"/>
-      <c r="AH30" s="39"/>
-      <c r="AI30" s="39"/>
-      <c r="AJ30" s="39"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="42"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="42"/>
+      <c r="W30" s="42"/>
+      <c r="X30" s="42"/>
+      <c r="Y30" s="42"/>
+      <c r="Z30" s="42"/>
+      <c r="AA30" s="42"/>
+      <c r="AB30" s="42"/>
+      <c r="AC30" s="42"/>
+      <c r="AD30" s="42"/>
+      <c r="AE30" s="42"/>
+      <c r="AF30" s="42"/>
+      <c r="AG30" s="42"/>
+      <c r="AH30" s="42"/>
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B31" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-      <c r="Z31" s="41"/>
-      <c r="AA31" s="41"/>
-      <c r="AB31" s="41"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="41"/>
-      <c r="AE31" s="41"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="41"/>
+      <c r="B31" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38"/>
+      <c r="AA31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31" s="38"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="38"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="38"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B32" s="38">
+      <c r="B32" s="40">
         <v>1</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="40"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="40"/>
-      <c r="U32" s="40"/>
-      <c r="V32" s="40"/>
-      <c r="W32" s="40"/>
-      <c r="X32" s="40"/>
-      <c r="Y32" s="40"/>
-      <c r="Z32" s="40"/>
-      <c r="AA32" s="40"/>
-      <c r="AB32" s="40"/>
-      <c r="AC32" s="40"/>
-      <c r="AD32" s="40"/>
-      <c r="AE32" s="40"/>
-      <c r="AF32" s="40"/>
-      <c r="AG32" s="40"/>
-      <c r="AH32" s="40"/>
-      <c r="AI32" s="40"/>
-      <c r="AJ32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="41"/>
+      <c r="AJ32" s="41"/>
     </row>
     <row r="33" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B33" s="38">
+      <c r="B33" s="40">
         <f>B32+1</f>
         <v>2</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="39"/>
-      <c r="S33" s="39"/>
-      <c r="T33" s="39"/>
-      <c r="U33" s="39"/>
-      <c r="V33" s="39"/>
-      <c r="W33" s="39"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="39"/>
-      <c r="AA33" s="39"/>
-      <c r="AB33" s="39"/>
-      <c r="AC33" s="39"/>
-      <c r="AD33" s="39"/>
-      <c r="AE33" s="39"/>
-      <c r="AF33" s="39"/>
-      <c r="AG33" s="39"/>
-      <c r="AH33" s="39"/>
-      <c r="AI33" s="39"/>
-      <c r="AJ33" s="39"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="42"/>
+      <c r="W33" s="42"/>
+      <c r="X33" s="42"/>
+      <c r="Y33" s="42"/>
+      <c r="Z33" s="42"/>
+      <c r="AA33" s="42"/>
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="42"/>
+      <c r="AD33" s="42"/>
+      <c r="AE33" s="42"/>
+      <c r="AF33" s="42"/>
+      <c r="AG33" s="42"/>
+      <c r="AH33" s="42"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="42"/>
     </row>
     <row r="34" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B34" s="38">
+      <c r="B34" s="40">
         <f>B33+1</f>
         <v>3</v>
       </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="39"/>
-      <c r="S34" s="39"/>
-      <c r="T34" s="39"/>
-      <c r="U34" s="39"/>
-      <c r="V34" s="39"/>
-      <c r="W34" s="39"/>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="39"/>
-      <c r="Z34" s="39"/>
-      <c r="AA34" s="39"/>
-      <c r="AB34" s="39"/>
-      <c r="AC34" s="39"/>
-      <c r="AD34" s="39"/>
-      <c r="AE34" s="39"/>
-      <c r="AF34" s="39"/>
-      <c r="AG34" s="39"/>
-      <c r="AH34" s="39"/>
-      <c r="AI34" s="39"/>
-      <c r="AJ34" s="39"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
+      <c r="X34" s="42"/>
+      <c r="Y34" s="42"/>
+      <c r="Z34" s="42"/>
+      <c r="AA34" s="42"/>
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="42"/>
+      <c r="AD34" s="42"/>
+      <c r="AE34" s="42"/>
+      <c r="AF34" s="42"/>
+      <c r="AG34" s="42"/>
+      <c r="AH34" s="42"/>
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="42"/>
     </row>
     <row r="35" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B35" s="38">
+      <c r="B35" s="40">
         <f>B34+1</f>
         <v>4</v>
       </c>
-      <c r="C35" s="38"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="40"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="40"/>
-      <c r="U35" s="40"/>
-      <c r="V35" s="40"/>
-      <c r="W35" s="40"/>
-      <c r="X35" s="40"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="40"/>
-      <c r="AA35" s="40"/>
-      <c r="AB35" s="40"/>
-      <c r="AC35" s="40"/>
-      <c r="AD35" s="40"/>
-      <c r="AE35" s="40"/>
-      <c r="AF35" s="40"/>
-      <c r="AG35" s="40"/>
-      <c r="AH35" s="40"/>
-      <c r="AI35" s="40"/>
-      <c r="AJ35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="41"/>
+      <c r="AJ35" s="41"/>
     </row>
     <row r="36" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B36" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
-      <c r="AC36" s="41"/>
-      <c r="AD36" s="41"/>
-      <c r="AE36" s="41"/>
-      <c r="AF36" s="41"/>
-      <c r="AG36" s="41"/>
-      <c r="AH36" s="41"/>
-      <c r="AI36" s="41"/>
-      <c r="AJ36" s="41"/>
+      <c r="B36" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="38"/>
     </row>
     <row r="37" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B37" s="38">
+      <c r="B37" s="40">
         <v>1</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="40"/>
-      <c r="V37" s="40"/>
-      <c r="W37" s="40"/>
-      <c r="X37" s="40"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="40"/>
-      <c r="AA37" s="40"/>
-      <c r="AB37" s="40"/>
-      <c r="AC37" s="40"/>
-      <c r="AD37" s="40"/>
-      <c r="AE37" s="40"/>
-      <c r="AF37" s="40"/>
-      <c r="AG37" s="40"/>
-      <c r="AH37" s="40"/>
-      <c r="AI37" s="40"/>
-      <c r="AJ37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="41"/>
+      <c r="Y37" s="41"/>
+      <c r="Z37" s="41"/>
+      <c r="AA37" s="41"/>
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="41"/>
+      <c r="AD37" s="41"/>
+      <c r="AE37" s="41"/>
+      <c r="AF37" s="41"/>
+      <c r="AG37" s="41"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="41"/>
+      <c r="AJ37" s="41"/>
     </row>
     <row r="38" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B38" s="38">
+      <c r="B38" s="40">
         <f>B37+1</f>
         <v>2</v>
       </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="39"/>
-      <c r="S38" s="39"/>
-      <c r="T38" s="39"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="39"/>
-      <c r="W38" s="39"/>
-      <c r="X38" s="39"/>
-      <c r="Y38" s="39"/>
-      <c r="Z38" s="39"/>
-      <c r="AA38" s="39"/>
-      <c r="AB38" s="39"/>
-      <c r="AC38" s="39"/>
-      <c r="AD38" s="39"/>
-      <c r="AE38" s="39"/>
-      <c r="AF38" s="39"/>
-      <c r="AG38" s="39"/>
-      <c r="AH38" s="39"/>
-      <c r="AI38" s="39"/>
-      <c r="AJ38" s="39"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="42"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="42"/>
+      <c r="V38" s="42"/>
+      <c r="W38" s="42"/>
+      <c r="X38" s="42"/>
+      <c r="Y38" s="42"/>
+      <c r="Z38" s="42"/>
+      <c r="AA38" s="42"/>
+      <c r="AB38" s="42"/>
+      <c r="AC38" s="42"/>
+      <c r="AD38" s="42"/>
+      <c r="AE38" s="42"/>
+      <c r="AF38" s="42"/>
+      <c r="AG38" s="42"/>
+      <c r="AH38" s="42"/>
+      <c r="AI38" s="42"/>
+      <c r="AJ38" s="42"/>
     </row>
     <row r="39" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B39" s="38">
+      <c r="B39" s="40">
         <f>B38+1</f>
         <v>3</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="39"/>
-      <c r="U39" s="39"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="39"/>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="39"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="39"/>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="39"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="39"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="42"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="42"/>
+      <c r="V39" s="42"/>
+      <c r="W39" s="42"/>
+      <c r="X39" s="42"/>
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AE39" s="42"/>
+      <c r="AF39" s="42"/>
+      <c r="AG39" s="42"/>
+      <c r="AH39" s="42"/>
+      <c r="AI39" s="42"/>
+      <c r="AJ39" s="42"/>
     </row>
     <row r="40" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B40" s="38">
+      <c r="B40" s="40">
         <f>B39+1</f>
         <v>4</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="39"/>
-      <c r="U40" s="39"/>
-      <c r="V40" s="39"/>
-      <c r="W40" s="39"/>
-      <c r="X40" s="39"/>
-      <c r="Y40" s="39"/>
-      <c r="Z40" s="39"/>
-      <c r="AA40" s="39"/>
-      <c r="AB40" s="39"/>
-      <c r="AC40" s="39"/>
-      <c r="AD40" s="39"/>
-      <c r="AE40" s="39"/>
-      <c r="AF40" s="39"/>
-      <c r="AG40" s="39"/>
-      <c r="AH40" s="39"/>
-      <c r="AI40" s="39"/>
-      <c r="AJ40" s="39"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="42"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="42"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="42"/>
+      <c r="V40" s="42"/>
+      <c r="W40" s="42"/>
+      <c r="X40" s="42"/>
+      <c r="Y40" s="42"/>
+      <c r="Z40" s="42"/>
+      <c r="AA40" s="42"/>
+      <c r="AB40" s="42"/>
+      <c r="AC40" s="42"/>
+      <c r="AD40" s="42"/>
+      <c r="AE40" s="42"/>
+      <c r="AF40" s="42"/>
+      <c r="AG40" s="42"/>
+      <c r="AH40" s="42"/>
+      <c r="AI40" s="42"/>
+      <c r="AJ40" s="42"/>
     </row>
     <row r="41" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B41" s="38">
+      <c r="B41" s="40">
         <f>B40+1</f>
         <v>5</v>
       </c>
-      <c r="C41" s="38"/>
-      <c r="D41" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="39"/>
-      <c r="U41" s="39"/>
-      <c r="V41" s="39"/>
-      <c r="W41" s="39"/>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="39"/>
-      <c r="Z41" s="39"/>
-      <c r="AA41" s="39"/>
-      <c r="AB41" s="39"/>
-      <c r="AC41" s="39"/>
-      <c r="AD41" s="39"/>
-      <c r="AE41" s="39"/>
-      <c r="AF41" s="39"/>
-      <c r="AG41" s="39"/>
-      <c r="AH41" s="39"/>
-      <c r="AI41" s="39"/>
-      <c r="AJ41" s="39"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="42"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="42"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="42"/>
+      <c r="V41" s="42"/>
+      <c r="W41" s="42"/>
+      <c r="X41" s="42"/>
+      <c r="Y41" s="42"/>
+      <c r="Z41" s="42"/>
+      <c r="AA41" s="42"/>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="42"/>
+      <c r="AD41" s="42"/>
+      <c r="AE41" s="42"/>
+      <c r="AF41" s="42"/>
+      <c r="AG41" s="42"/>
+      <c r="AH41" s="42"/>
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="42"/>
     </row>
     <row r="42" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B42" s="38">
+      <c r="B42" s="40">
         <f>B41+1</f>
         <v>6</v>
       </c>
-      <c r="C42" s="38"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="40"/>
-      <c r="L42" s="40"/>
-      <c r="M42" s="40"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="40"/>
-      <c r="S42" s="40"/>
-      <c r="T42" s="40"/>
-      <c r="U42" s="40"/>
-      <c r="V42" s="40"/>
-      <c r="W42" s="40"/>
-      <c r="X42" s="40"/>
-      <c r="Y42" s="40"/>
-      <c r="Z42" s="40"/>
-      <c r="AA42" s="40"/>
-      <c r="AB42" s="40"/>
-      <c r="AC42" s="40"/>
-      <c r="AD42" s="40"/>
-      <c r="AE42" s="40"/>
-      <c r="AF42" s="40"/>
-      <c r="AG42" s="40"/>
-      <c r="AH42" s="40"/>
-      <c r="AI42" s="40"/>
-      <c r="AJ42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
+      <c r="W42" s="41"/>
+      <c r="X42" s="41"/>
+      <c r="Y42" s="41"/>
+      <c r="Z42" s="41"/>
+      <c r="AA42" s="41"/>
+      <c r="AB42" s="41"/>
+      <c r="AC42" s="41"/>
+      <c r="AD42" s="41"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
+      <c r="AI42" s="41"/>
+      <c r="AJ42" s="41"/>
     </row>
     <row r="43" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B43" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="41"/>
-      <c r="Z43" s="41"/>
-      <c r="AA43" s="41"/>
-      <c r="AB43" s="41"/>
-      <c r="AC43" s="41"/>
-      <c r="AD43" s="41"/>
-      <c r="AE43" s="41"/>
-      <c r="AF43" s="41"/>
-      <c r="AG43" s="41"/>
-      <c r="AH43" s="41"/>
-      <c r="AI43" s="41"/>
-      <c r="AJ43" s="41"/>
+      <c r="B43" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="38"/>
+      <c r="Y43" s="38"/>
+      <c r="Z43" s="38"/>
+      <c r="AA43" s="38"/>
+      <c r="AB43" s="38"/>
+      <c r="AC43" s="38"/>
+      <c r="AD43" s="38"/>
+      <c r="AE43" s="38"/>
+      <c r="AF43" s="38"/>
+      <c r="AG43" s="38"/>
+      <c r="AH43" s="38"/>
+      <c r="AI43" s="38"/>
+      <c r="AJ43" s="38"/>
     </row>
     <row r="44" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B44" s="38">
+      <c r="B44" s="40">
         <v>1</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="39"/>
-      <c r="U44" s="39"/>
-      <c r="V44" s="39"/>
-      <c r="W44" s="39"/>
-      <c r="X44" s="39"/>
-      <c r="Y44" s="39"/>
-      <c r="Z44" s="39"/>
-      <c r="AA44" s="39"/>
-      <c r="AB44" s="39"/>
-      <c r="AC44" s="39"/>
-      <c r="AD44" s="39"/>
-      <c r="AE44" s="39"/>
-      <c r="AF44" s="39"/>
-      <c r="AG44" s="39"/>
-      <c r="AH44" s="39"/>
-      <c r="AI44" s="39"/>
-      <c r="AJ44" s="39"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="42"/>
+      <c r="X44" s="42"/>
+      <c r="Y44" s="42"/>
+      <c r="Z44" s="42"/>
+      <c r="AA44" s="42"/>
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="42"/>
+      <c r="AD44" s="42"/>
+      <c r="AE44" s="42"/>
+      <c r="AF44" s="42"/>
+      <c r="AG44" s="42"/>
+      <c r="AH44" s="42"/>
+      <c r="AI44" s="42"/>
+      <c r="AJ44" s="42"/>
     </row>
     <row r="45" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B45" s="38">
+      <c r="B45" s="40">
         <f>B44+1</f>
         <v>2</v>
       </c>
-      <c r="C45" s="38"/>
-      <c r="D45" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="39"/>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="39"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="39"/>
-      <c r="U45" s="39"/>
-      <c r="V45" s="39"/>
-      <c r="W45" s="39"/>
-      <c r="X45" s="39"/>
-      <c r="Y45" s="39"/>
-      <c r="Z45" s="39"/>
-      <c r="AA45" s="39"/>
-      <c r="AB45" s="39"/>
-      <c r="AC45" s="39"/>
-      <c r="AD45" s="39"/>
-      <c r="AE45" s="39"/>
-      <c r="AF45" s="39"/>
-      <c r="AG45" s="39"/>
-      <c r="AH45" s="39"/>
-      <c r="AI45" s="39"/>
-      <c r="AJ45" s="39"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="42"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="42"/>
+      <c r="W45" s="42"/>
+      <c r="X45" s="42"/>
+      <c r="Y45" s="42"/>
+      <c r="Z45" s="42"/>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="42"/>
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="42"/>
+      <c r="AF45" s="42"/>
+      <c r="AG45" s="42"/>
+      <c r="AH45" s="42"/>
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="42"/>
     </row>
     <row r="46" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B46" s="38">
+      <c r="B46" s="40">
         <f>B45+1</f>
         <v>3</v>
       </c>
-      <c r="C46" s="38"/>
-      <c r="D46" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="39"/>
-      <c r="M46" s="39"/>
-      <c r="N46" s="39"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="39"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="39"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="39"/>
-      <c r="U46" s="39"/>
-      <c r="V46" s="39"/>
-      <c r="W46" s="39"/>
-      <c r="X46" s="39"/>
-      <c r="Y46" s="39"/>
-      <c r="Z46" s="39"/>
-      <c r="AA46" s="39"/>
-      <c r="AB46" s="39"/>
-      <c r="AC46" s="39"/>
-      <c r="AD46" s="39"/>
-      <c r="AE46" s="39"/>
-      <c r="AF46" s="39"/>
-      <c r="AG46" s="39"/>
-      <c r="AH46" s="39"/>
-      <c r="AI46" s="39"/>
-      <c r="AJ46" s="39"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="42"/>
+      <c r="O46" s="42"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="42"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="42"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="42"/>
+      <c r="V46" s="42"/>
+      <c r="W46" s="42"/>
+      <c r="X46" s="42"/>
+      <c r="Y46" s="42"/>
+      <c r="Z46" s="42"/>
+      <c r="AA46" s="42"/>
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="42"/>
+      <c r="AD46" s="42"/>
+      <c r="AE46" s="42"/>
+      <c r="AF46" s="42"/>
+      <c r="AG46" s="42"/>
+      <c r="AH46" s="42"/>
+      <c r="AI46" s="42"/>
+      <c r="AJ46" s="42"/>
     </row>
     <row r="47" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B47" s="38">
+      <c r="B47" s="40">
         <f>B46+1</f>
         <v>4</v>
       </c>
-      <c r="C47" s="38"/>
-      <c r="D47" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
-      <c r="N47" s="39"/>
-      <c r="O47" s="39"/>
-      <c r="P47" s="39"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="39"/>
-      <c r="S47" s="39"/>
-      <c r="T47" s="39"/>
-      <c r="U47" s="39"/>
-      <c r="V47" s="39"/>
-      <c r="W47" s="39"/>
-      <c r="X47" s="39"/>
-      <c r="Y47" s="39"/>
-      <c r="Z47" s="39"/>
-      <c r="AA47" s="39"/>
-      <c r="AB47" s="39"/>
-      <c r="AC47" s="39"/>
-      <c r="AD47" s="39"/>
-      <c r="AE47" s="39"/>
-      <c r="AF47" s="39"/>
-      <c r="AG47" s="39"/>
-      <c r="AH47" s="39"/>
-      <c r="AI47" s="39"/>
-      <c r="AJ47" s="39"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
+      <c r="N47" s="42"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="42"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="42"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="42"/>
+      <c r="V47" s="42"/>
+      <c r="W47" s="42"/>
+      <c r="X47" s="42"/>
+      <c r="Y47" s="42"/>
+      <c r="Z47" s="42"/>
+      <c r="AA47" s="42"/>
+      <c r="AB47" s="42"/>
+      <c r="AC47" s="42"/>
+      <c r="AD47" s="42"/>
+      <c r="AE47" s="42"/>
+      <c r="AF47" s="42"/>
+      <c r="AG47" s="42"/>
+      <c r="AH47" s="42"/>
+      <c r="AI47" s="42"/>
+      <c r="AJ47" s="42"/>
     </row>
     <row r="48" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B48" s="38">
+      <c r="B48" s="40">
         <f>B47+1</f>
         <v>5</v>
       </c>
-      <c r="C48" s="38"/>
-      <c r="D48" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="40"/>
-      <c r="U48" s="40"/>
-      <c r="V48" s="40"/>
-      <c r="W48" s="40"/>
-      <c r="X48" s="40"/>
-      <c r="Y48" s="40"/>
-      <c r="Z48" s="40"/>
-      <c r="AA48" s="40"/>
-      <c r="AB48" s="40"/>
-      <c r="AC48" s="40"/>
-      <c r="AD48" s="40"/>
-      <c r="AE48" s="40"/>
-      <c r="AF48" s="40"/>
-      <c r="AG48" s="40"/>
-      <c r="AH48" s="40"/>
-      <c r="AI48" s="40"/>
-      <c r="AJ48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="41"/>
+      <c r="M48" s="41"/>
+      <c r="N48" s="41"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="41"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="41"/>
+      <c r="W48" s="41"/>
+      <c r="X48" s="41"/>
+      <c r="Y48" s="41"/>
+      <c r="Z48" s="41"/>
+      <c r="AA48" s="41"/>
+      <c r="AB48" s="41"/>
+      <c r="AC48" s="41"/>
+      <c r="AD48" s="41"/>
+      <c r="AE48" s="41"/>
+      <c r="AF48" s="41"/>
+      <c r="AG48" s="41"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="41"/>
+      <c r="AJ48" s="41"/>
     </row>
     <row r="49" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B49" s="38">
+      <c r="B49" s="40">
         <f>B48+1</f>
         <v>6</v>
       </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-      <c r="Q49" s="40"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="40"/>
-      <c r="U49" s="40"/>
-      <c r="V49" s="40"/>
-      <c r="W49" s="40"/>
-      <c r="X49" s="40"/>
-      <c r="Y49" s="40"/>
-      <c r="Z49" s="40"/>
-      <c r="AA49" s="40"/>
-      <c r="AB49" s="40"/>
-      <c r="AC49" s="40"/>
-      <c r="AD49" s="40"/>
-      <c r="AE49" s="40"/>
-      <c r="AF49" s="40"/>
-      <c r="AG49" s="40"/>
-      <c r="AH49" s="40"/>
-      <c r="AI49" s="40"/>
-      <c r="AJ49" s="40"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="41"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="41"/>
+      <c r="T49" s="41"/>
+      <c r="U49" s="41"/>
+      <c r="V49" s="41"/>
+      <c r="W49" s="41"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="41"/>
+      <c r="Z49" s="41"/>
+      <c r="AA49" s="41"/>
+      <c r="AB49" s="41"/>
+      <c r="AC49" s="41"/>
+      <c r="AD49" s="41"/>
+      <c r="AE49" s="41"/>
+      <c r="AF49" s="41"/>
+      <c r="AG49" s="41"/>
+      <c r="AH49" s="41"/>
+      <c r="AI49" s="41"/>
+      <c r="AJ49" s="41"/>
     </row>
     <row r="50" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B50" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
-      <c r="X50" s="41"/>
-      <c r="Y50" s="41"/>
-      <c r="Z50" s="41"/>
-      <c r="AA50" s="41"/>
-      <c r="AB50" s="41"/>
-      <c r="AC50" s="41"/>
-      <c r="AD50" s="41"/>
-      <c r="AE50" s="41"/>
-      <c r="AF50" s="41"/>
-      <c r="AG50" s="41"/>
-      <c r="AH50" s="41"/>
-      <c r="AI50" s="41"/>
-      <c r="AJ50" s="41"/>
+      <c r="B50" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="38"/>
+      <c r="T50" s="38"/>
+      <c r="U50" s="38"/>
+      <c r="V50" s="38"/>
+      <c r="W50" s="38"/>
+      <c r="X50" s="38"/>
+      <c r="Y50" s="38"/>
+      <c r="Z50" s="38"/>
+      <c r="AA50" s="38"/>
+      <c r="AB50" s="38"/>
+      <c r="AC50" s="38"/>
+      <c r="AD50" s="38"/>
+      <c r="AE50" s="38"/>
+      <c r="AF50" s="38"/>
+      <c r="AG50" s="38"/>
+      <c r="AH50" s="38"/>
+      <c r="AI50" s="38"/>
+      <c r="AJ50" s="38"/>
     </row>
     <row r="51" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B51" s="38">
+      <c r="B51" s="40">
         <v>1</v>
       </c>
-      <c r="C51" s="38"/>
-      <c r="D51" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="39"/>
-      <c r="O51" s="39"/>
-      <c r="P51" s="39"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="39"/>
-      <c r="S51" s="39"/>
-      <c r="T51" s="39"/>
-      <c r="U51" s="39"/>
-      <c r="V51" s="39"/>
-      <c r="W51" s="39"/>
-      <c r="X51" s="39"/>
-      <c r="Y51" s="39"/>
-      <c r="Z51" s="39"/>
-      <c r="AA51" s="39"/>
-      <c r="AB51" s="39"/>
-      <c r="AC51" s="39"/>
-      <c r="AD51" s="39"/>
-      <c r="AE51" s="39"/>
-      <c r="AF51" s="39"/>
-      <c r="AG51" s="39"/>
-      <c r="AH51" s="39"/>
-      <c r="AI51" s="39"/>
-      <c r="AJ51" s="39"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
+      <c r="N51" s="42"/>
+      <c r="O51" s="42"/>
+      <c r="P51" s="42"/>
+      <c r="Q51" s="42"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="42"/>
+      <c r="T51" s="42"/>
+      <c r="U51" s="42"/>
+      <c r="V51" s="42"/>
+      <c r="W51" s="42"/>
+      <c r="X51" s="42"/>
+      <c r="Y51" s="42"/>
+      <c r="Z51" s="42"/>
+      <c r="AA51" s="42"/>
+      <c r="AB51" s="42"/>
+      <c r="AC51" s="42"/>
+      <c r="AD51" s="42"/>
+      <c r="AE51" s="42"/>
+      <c r="AF51" s="42"/>
+      <c r="AG51" s="42"/>
+      <c r="AH51" s="42"/>
+      <c r="AI51" s="42"/>
+      <c r="AJ51" s="42"/>
     </row>
     <row r="52" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B52" s="38">
+      <c r="B52" s="40">
         <f>B51+1</f>
         <v>2</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
-      <c r="T52" s="39"/>
-      <c r="U52" s="39"/>
-      <c r="V52" s="39"/>
-      <c r="W52" s="39"/>
-      <c r="X52" s="39"/>
-      <c r="Y52" s="39"/>
-      <c r="Z52" s="39"/>
-      <c r="AA52" s="39"/>
-      <c r="AB52" s="39"/>
-      <c r="AC52" s="39"/>
-      <c r="AD52" s="39"/>
-      <c r="AE52" s="39"/>
-      <c r="AF52" s="39"/>
-      <c r="AG52" s="39"/>
-      <c r="AH52" s="39"/>
-      <c r="AI52" s="39"/>
-      <c r="AJ52" s="39"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42"/>
+      <c r="M52" s="42"/>
+      <c r="N52" s="42"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="42"/>
+      <c r="R52" s="42"/>
+      <c r="S52" s="42"/>
+      <c r="T52" s="42"/>
+      <c r="U52" s="42"/>
+      <c r="V52" s="42"/>
+      <c r="W52" s="42"/>
+      <c r="X52" s="42"/>
+      <c r="Y52" s="42"/>
+      <c r="Z52" s="42"/>
+      <c r="AA52" s="42"/>
+      <c r="AB52" s="42"/>
+      <c r="AC52" s="42"/>
+      <c r="AD52" s="42"/>
+      <c r="AE52" s="42"/>
+      <c r="AF52" s="42"/>
+      <c r="AG52" s="42"/>
+      <c r="AH52" s="42"/>
+      <c r="AI52" s="42"/>
+      <c r="AJ52" s="42"/>
     </row>
     <row r="53" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B53" s="38">
+      <c r="B53" s="40">
         <f>B52+1</f>
         <v>3</v>
       </c>
-      <c r="C53" s="38"/>
-      <c r="D53" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
-      <c r="P53" s="39"/>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="39"/>
-      <c r="S53" s="39"/>
-      <c r="T53" s="39"/>
-      <c r="U53" s="39"/>
-      <c r="V53" s="39"/>
-      <c r="W53" s="39"/>
-      <c r="X53" s="39"/>
-      <c r="Y53" s="39"/>
-      <c r="Z53" s="39"/>
-      <c r="AA53" s="39"/>
-      <c r="AB53" s="39"/>
-      <c r="AC53" s="39"/>
-      <c r="AD53" s="39"/>
-      <c r="AE53" s="39"/>
-      <c r="AF53" s="39"/>
-      <c r="AG53" s="39"/>
-      <c r="AH53" s="39"/>
-      <c r="AI53" s="39"/>
-      <c r="AJ53" s="39"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="42"/>
+      <c r="O53" s="42"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="42"/>
+      <c r="R53" s="42"/>
+      <c r="S53" s="42"/>
+      <c r="T53" s="42"/>
+      <c r="U53" s="42"/>
+      <c r="V53" s="42"/>
+      <c r="W53" s="42"/>
+      <c r="X53" s="42"/>
+      <c r="Y53" s="42"/>
+      <c r="Z53" s="42"/>
+      <c r="AA53" s="42"/>
+      <c r="AB53" s="42"/>
+      <c r="AC53" s="42"/>
+      <c r="AD53" s="42"/>
+      <c r="AE53" s="42"/>
+      <c r="AF53" s="42"/>
+      <c r="AG53" s="42"/>
+      <c r="AH53" s="42"/>
+      <c r="AI53" s="42"/>
+      <c r="AJ53" s="42"/>
     </row>
     <row r="54" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B54" s="38">
+      <c r="B54" s="40">
         <f>B53+1</f>
         <v>4</v>
       </c>
-      <c r="C54" s="38"/>
-      <c r="D54" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="39"/>
-      <c r="O54" s="39"/>
-      <c r="P54" s="39"/>
-      <c r="Q54" s="39"/>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39"/>
-      <c r="T54" s="39"/>
-      <c r="U54" s="39"/>
-      <c r="V54" s="39"/>
-      <c r="W54" s="39"/>
-      <c r="X54" s="39"/>
-      <c r="Y54" s="39"/>
-      <c r="Z54" s="39"/>
-      <c r="AA54" s="39"/>
-      <c r="AB54" s="39"/>
-      <c r="AC54" s="39"/>
-      <c r="AD54" s="39"/>
-      <c r="AE54" s="39"/>
-      <c r="AF54" s="39"/>
-      <c r="AG54" s="39"/>
-      <c r="AH54" s="39"/>
-      <c r="AI54" s="39"/>
-      <c r="AJ54" s="39"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
+      <c r="N54" s="42"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="42"/>
+      <c r="R54" s="42"/>
+      <c r="S54" s="42"/>
+      <c r="T54" s="42"/>
+      <c r="U54" s="42"/>
+      <c r="V54" s="42"/>
+      <c r="W54" s="42"/>
+      <c r="X54" s="42"/>
+      <c r="Y54" s="42"/>
+      <c r="Z54" s="42"/>
+      <c r="AA54" s="42"/>
+      <c r="AB54" s="42"/>
+      <c r="AC54" s="42"/>
+      <c r="AD54" s="42"/>
+      <c r="AE54" s="42"/>
+      <c r="AF54" s="42"/>
+      <c r="AG54" s="42"/>
+      <c r="AH54" s="42"/>
+      <c r="AI54" s="42"/>
+      <c r="AJ54" s="42"/>
     </row>
     <row r="55" spans="2:36" x14ac:dyDescent="0.15">
-      <c r="B55" s="38">
+      <c r="B55" s="40">
         <f>B54+1</f>
         <v>5</v>
       </c>
-      <c r="C55" s="38"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="39"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="39"/>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39"/>
-      <c r="T55" s="39"/>
-      <c r="U55" s="39"/>
-      <c r="V55" s="39"/>
-      <c r="W55" s="39"/>
-      <c r="X55" s="39"/>
-      <c r="Y55" s="39"/>
-      <c r="Z55" s="39"/>
-      <c r="AA55" s="39"/>
-      <c r="AB55" s="39"/>
-      <c r="AC55" s="39"/>
-      <c r="AD55" s="39"/>
-      <c r="AE55" s="39"/>
-      <c r="AF55" s="39"/>
-      <c r="AG55" s="39"/>
-      <c r="AH55" s="39"/>
-      <c r="AI55" s="39"/>
-      <c r="AJ55" s="39"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
+      <c r="N55" s="42"/>
+      <c r="O55" s="42"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="42"/>
+      <c r="R55" s="42"/>
+      <c r="S55" s="42"/>
+      <c r="T55" s="42"/>
+      <c r="U55" s="42"/>
+      <c r="V55" s="42"/>
+      <c r="W55" s="42"/>
+      <c r="X55" s="42"/>
+      <c r="Y55" s="42"/>
+      <c r="Z55" s="42"/>
+      <c r="AA55" s="42"/>
+      <c r="AB55" s="42"/>
+      <c r="AC55" s="42"/>
+      <c r="AD55" s="42"/>
+      <c r="AE55" s="42"/>
+      <c r="AF55" s="42"/>
+      <c r="AG55" s="42"/>
+      <c r="AH55" s="42"/>
+      <c r="AI55" s="42"/>
+      <c r="AJ55" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="B4:AJ4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:AJ5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:AJ6"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:AJ9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:AJ10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:AJ7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:AJ8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:AJ13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:AJ14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:AJ11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:AJ12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:AJ15"/>
-    <mergeCell ref="B16:AJ16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:AJ17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:AJ18"/>
-    <mergeCell ref="B19:AJ19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:AJ20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:AJ23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:AJ24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:AJ21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:AJ22"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:AJ54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:AJ55"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:AJ52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:AJ53"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:AJ49"/>
+    <mergeCell ref="B50:AJ50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:AJ51"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:AJ47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:AJ48"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:AJ45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:AJ46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:AJ42"/>
+    <mergeCell ref="B43:AJ43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:AJ44"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:AJ40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:AJ41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:AJ38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:AJ39"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:AJ35"/>
+    <mergeCell ref="B36:AJ36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:AJ37"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:AJ33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:AJ34"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:AJ30"/>
+    <mergeCell ref="B31:AJ31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:AJ32"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:AJ28"/>
     <mergeCell ref="B29:C29"/>
@@ -10862,54 +10638,45 @@
     <mergeCell ref="B26:AJ26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:AJ27"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:AJ33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:AJ34"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:AJ30"/>
-    <mergeCell ref="B31:AJ31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:AJ32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:AJ35"/>
-    <mergeCell ref="B36:AJ36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:AJ37"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:AJ40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:AJ41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:AJ38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:AJ39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:AJ42"/>
-    <mergeCell ref="B43:AJ43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:AJ44"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:AJ47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:AJ48"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:AJ45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:AJ46"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:AJ49"/>
-    <mergeCell ref="B50:AJ50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:AJ51"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:AJ54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:AJ55"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:AJ52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:AJ53"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:AJ23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:AJ24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:AJ21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:AJ22"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:AJ18"/>
+    <mergeCell ref="B19:AJ19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:AJ20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:AJ15"/>
+    <mergeCell ref="B16:AJ16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:AJ17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:AJ13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:AJ14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:AJ11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:AJ12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:AJ9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:AJ10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:AJ7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:AJ8"/>
+    <mergeCell ref="B4:AJ4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:AJ5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:AJ6"/>
   </mergeCells>
   <phoneticPr fontId="32"/>
   <conditionalFormatting sqref="B6:AJ15 B17:AJ18 B20:AJ25 B27:AJ30 B32:AJ35 B37:AJ42 B44:AJ49 B51:AJ55">
@@ -10978,12 +10745,12 @@
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B3" s="68" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" s="68"/>
       <c r="D3" s="68"/>
@@ -11005,58 +10772,58 @@
     </row>
     <row r="4" spans="2:19" ht="37.5" x14ac:dyDescent="0.15">
       <c r="B4" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="E4" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="F4" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="G4" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="H4" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="I4" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="J4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="K4" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="L4" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="M4" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="N4" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="31" t="s">
+      <c r="O4" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="P4" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="31" t="s">
+      <c r="Q4" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="31" t="s">
+      <c r="R4" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>68</v>
-      </c>
-      <c r="R4" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" s="32" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="37.5" x14ac:dyDescent="0.15">
@@ -11064,13 +10831,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>71</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>73</v>
       </c>
       <c r="F5" s="33">
         <v>0</v>
@@ -11100,29 +10867,29 @@
         <v>44295.498003877299</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R5" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S5" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:19" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B7" s="68" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
@@ -11144,58 +10911,58 @@
     </row>
     <row r="8" spans="2:19" ht="37.5" x14ac:dyDescent="0.15">
       <c r="B8" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="F8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="G8" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="H8" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="I8" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="J8" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="K8" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="L8" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="M8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="N8" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="O8" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="P8" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="31" t="s">
+      <c r="Q8" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="R8" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="Q8" s="32" t="s">
+      <c r="S8" s="32" t="s">
         <v>68</v>
-      </c>
-      <c r="R8" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="S8" s="32" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="37.5" x14ac:dyDescent="0.15">
@@ -11203,13 +10970,13 @@
         <v>16</v>
       </c>
       <c r="C9" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>71</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>73</v>
       </c>
       <c r="F9" s="33">
         <v>0</v>
@@ -11239,19 +11006,19 @@
         <v>44295.542262476898</v>
       </c>
       <c r="O9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -11694,32 +11461,32 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="7"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="45"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="45"/>
-      <c r="AD8" s="45"/>
-      <c r="AE8" s="45"/>
-      <c r="AF8" s="45"/>
-      <c r="AG8" s="45"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="45"/>
-      <c r="AJ8" s="45"/>
-      <c r="AK8" s="45"/>
-      <c r="AL8" s="45"/>
-      <c r="AM8" s="45"/>
-      <c r="AN8" s="45"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
+      <c r="Z8" s="43"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="43"/>
+      <c r="AE8" s="43"/>
+      <c r="AF8" s="43"/>
+      <c r="AG8" s="43"/>
+      <c r="AH8" s="43"/>
+      <c r="AI8" s="43"/>
+      <c r="AJ8" s="43"/>
+      <c r="AK8" s="43"/>
+      <c r="AL8" s="43"/>
+      <c r="AM8" s="43"/>
+      <c r="AN8" s="43"/>
       <c r="AO8" s="8"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
@@ -11751,34 +11518,34 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="49" t="s">
+      <c r="O9" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="44"/>
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="44"/>
+      <c r="AK9" s="44"/>
+      <c r="AL9" s="44"/>
+      <c r="AM9" s="44"/>
+      <c r="AN9" s="44"/>
       <c r="AO9" s="8"/>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="2"/>
@@ -11810,34 +11577,34 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="49"/>
-      <c r="AG10" s="49"/>
-      <c r="AH10" s="49"/>
-      <c r="AI10" s="49"/>
-      <c r="AJ10" s="49"/>
-      <c r="AK10" s="49"/>
-      <c r="AL10" s="49"/>
-      <c r="AM10" s="49"/>
-      <c r="AN10" s="49"/>
+      <c r="O10" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="44"/>
+      <c r="AF10" s="44"/>
+      <c r="AG10" s="44"/>
+      <c r="AH10" s="44"/>
+      <c r="AI10" s="44"/>
+      <c r="AJ10" s="44"/>
+      <c r="AK10" s="44"/>
+      <c r="AL10" s="44"/>
+      <c r="AM10" s="44"/>
+      <c r="AN10" s="44"/>
       <c r="AO10" s="8"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="2"/>
@@ -11930,26 +11697,26 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
-      <c r="S12" s="50" t="s">
+      <c r="S12" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
-      <c r="AA12" s="50"/>
-      <c r="AB12" s="50"/>
-      <c r="AC12" s="50"/>
-      <c r="AD12" s="50"/>
-      <c r="AE12" s="50"/>
-      <c r="AF12" s="50"/>
-      <c r="AG12" s="50"/>
-      <c r="AH12" s="50"/>
-      <c r="AI12" s="50"/>
-      <c r="AJ12" s="50"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
       <c r="AK12" s="2"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
@@ -11989,26 +11756,26 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="S13" s="50" t="s">
+      <c r="S13" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="50"/>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="50"/>
-      <c r="AE13" s="50"/>
-      <c r="AF13" s="50"/>
-      <c r="AG13" s="50"/>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-      <c r="AJ13" s="50"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="45"/>
+      <c r="AA13" s="45"/>
+      <c r="AB13" s="45"/>
+      <c r="AC13" s="45"/>
+      <c r="AD13" s="45"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="45"/>
+      <c r="AJ13" s="45"/>
       <c r="AK13" s="2"/>
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
@@ -12113,12 +11880,12 @@
       <c r="X15" s="12"/>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="45"/>
-      <c r="AC15" s="45"/>
-      <c r="AD15" s="45"/>
-      <c r="AE15" s="45"/>
-      <c r="AF15" s="45"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="43"/>
+      <c r="AE15" s="43"/>
+      <c r="AF15" s="43"/>
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
@@ -12226,7 +11993,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2" t="str">
         <f>"第"&amp;TEXT(MAX(更新履歴!A8:I31),"#0.0")&amp;"版"</f>
-        <v>第1.1版</v>
+        <v>第1.0版</v>
       </c>
       <c r="Y17" s="14"/>
       <c r="Z17" s="14"/>
@@ -12347,12 +12114,12 @@
       <c r="X19" s="16"/>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
-      <c r="AA19" s="45"/>
-      <c r="AB19" s="45"/>
-      <c r="AC19" s="45"/>
-      <c r="AD19" s="45"/>
-      <c r="AE19" s="45"/>
-      <c r="AF19" s="45"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="43"/>
+      <c r="AF19" s="43"/>
       <c r="AG19" s="17"/>
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
@@ -12457,23 +12224,23 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="V21" s="43"/>
-      <c r="W21" s="43"/>
-      <c r="X21" s="43"/>
-      <c r="Y21" s="43"/>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="44"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="44"/>
-      <c r="AF21" s="44"/>
-      <c r="AG21" s="44"/>
-      <c r="AH21" s="44"/>
-      <c r="AI21" s="44"/>
+      <c r="U21" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="50"/>
+      <c r="AA21" s="50"/>
+      <c r="AB21" s="50"/>
+      <c r="AC21" s="50"/>
+      <c r="AD21" s="50"/>
+      <c r="AE21" s="50"/>
+      <c r="AF21" s="50"/>
+      <c r="AG21" s="50"/>
+      <c r="AH21" s="50"/>
+      <c r="AI21" s="50"/>
       <c r="AJ21" s="2"/>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
@@ -12514,21 +12281,21 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="44"/>
-      <c r="AE22" s="44"/>
-      <c r="AF22" s="44"/>
-      <c r="AG22" s="44"/>
-      <c r="AH22" s="44"/>
-      <c r="AI22" s="44"/>
+      <c r="U22" s="49"/>
+      <c r="V22" s="49"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="49"/>
+      <c r="Y22" s="49"/>
+      <c r="Z22" s="50"/>
+      <c r="AA22" s="50"/>
+      <c r="AB22" s="50"/>
+      <c r="AC22" s="50"/>
+      <c r="AD22" s="50"/>
+      <c r="AE22" s="50"/>
+      <c r="AF22" s="50"/>
+      <c r="AG22" s="50"/>
+      <c r="AH22" s="50"/>
+      <c r="AI22" s="50"/>
       <c r="AJ22" s="2"/>
       <c r="AK22" s="2"/>
       <c r="AL22" s="2"/>
@@ -12569,21 +12336,21 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
-      <c r="AC23" s="44"/>
-      <c r="AD23" s="44"/>
-      <c r="AE23" s="44"/>
-      <c r="AF23" s="44"/>
-      <c r="AG23" s="44"/>
-      <c r="AH23" s="44"/>
-      <c r="AI23" s="44"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="50"/>
+      <c r="AA23" s="50"/>
+      <c r="AB23" s="50"/>
+      <c r="AC23" s="50"/>
+      <c r="AD23" s="50"/>
+      <c r="AE23" s="50"/>
+      <c r="AF23" s="50"/>
+      <c r="AG23" s="50"/>
+      <c r="AH23" s="50"/>
+      <c r="AI23" s="50"/>
       <c r="AJ23" s="2"/>
       <c r="AK23" s="2"/>
       <c r="AL23" s="2"/>
@@ -12624,21 +12391,21 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="43"/>
-      <c r="Y24" s="43"/>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="44"/>
-      <c r="AC24" s="44"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="44"/>
-      <c r="AF24" s="44"/>
-      <c r="AG24" s="44"/>
-      <c r="AH24" s="44"/>
-      <c r="AI24" s="44"/>
+      <c r="U24" s="49"/>
+      <c r="V24" s="49"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="49"/>
+      <c r="Y24" s="49"/>
+      <c r="Z24" s="50"/>
+      <c r="AA24" s="50"/>
+      <c r="AB24" s="50"/>
+      <c r="AC24" s="50"/>
+      <c r="AD24" s="50"/>
+      <c r="AE24" s="50"/>
+      <c r="AF24" s="50"/>
+      <c r="AG24" s="50"/>
+      <c r="AH24" s="50"/>
+      <c r="AI24" s="50"/>
       <c r="AJ24" s="2"/>
       <c r="AK24" s="2"/>
       <c r="AL24" s="2"/>
@@ -13117,24 +12884,24 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="45"/>
-      <c r="AC33" s="45"/>
-      <c r="AD33" s="45"/>
-      <c r="AE33" s="45"/>
-      <c r="AF33" s="45"/>
-      <c r="AG33" s="45"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="45"/>
-      <c r="AJ33" s="45"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
+      <c r="X33" s="43"/>
+      <c r="Y33" s="43"/>
+      <c r="Z33" s="43"/>
+      <c r="AA33" s="43"/>
+      <c r="AB33" s="43"/>
+      <c r="AC33" s="43"/>
+      <c r="AD33" s="43"/>
+      <c r="AE33" s="43"/>
+      <c r="AF33" s="43"/>
+      <c r="AG33" s="43"/>
+      <c r="AH33" s="43"/>
+      <c r="AI33" s="43"/>
+      <c r="AJ33" s="43"/>
       <c r="AK33" s="2"/>
       <c r="AL33" s="2"/>
       <c r="AM33" s="2"/>
@@ -13172,24 +12939,24 @@
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="45"/>
-      <c r="AB34" s="45"/>
-      <c r="AC34" s="45"/>
-      <c r="AD34" s="45"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="45"/>
-      <c r="AJ34" s="45"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="43"/>
+      <c r="Y34" s="43"/>
+      <c r="Z34" s="43"/>
+      <c r="AA34" s="43"/>
+      <c r="AB34" s="43"/>
+      <c r="AC34" s="43"/>
+      <c r="AD34" s="43"/>
+      <c r="AE34" s="43"/>
+      <c r="AF34" s="43"/>
+      <c r="AG34" s="43"/>
+      <c r="AH34" s="43"/>
+      <c r="AI34" s="43"/>
+      <c r="AJ34" s="43"/>
       <c r="AK34" s="2"/>
       <c r="AL34" s="2"/>
       <c r="AM34" s="2"/>
@@ -13227,24 +12994,24 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45"/>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45"/>
-      <c r="W35" s="45"/>
-      <c r="X35" s="45"/>
-      <c r="Y35" s="45"/>
-      <c r="Z35" s="45"/>
-      <c r="AA35" s="45"/>
-      <c r="AB35" s="45"/>
-      <c r="AC35" s="45"/>
-      <c r="AD35" s="45"/>
-      <c r="AE35" s="45"/>
-      <c r="AF35" s="45"/>
-      <c r="AG35" s="45"/>
-      <c r="AH35" s="45"/>
-      <c r="AI35" s="45"/>
-      <c r="AJ35" s="45"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="43"/>
+      <c r="Y35" s="43"/>
+      <c r="Z35" s="43"/>
+      <c r="AA35" s="43"/>
+      <c r="AB35" s="43"/>
+      <c r="AC35" s="43"/>
+      <c r="AD35" s="43"/>
+      <c r="AE35" s="43"/>
+      <c r="AF35" s="43"/>
+      <c r="AG35" s="43"/>
+      <c r="AH35" s="43"/>
+      <c r="AI35" s="43"/>
+      <c r="AJ35" s="43"/>
       <c r="AK35" s="2"/>
       <c r="AL35" s="2"/>
       <c r="AM35" s="2"/>
@@ -13430,22 +13197,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="O8:AN8"/>
-    <mergeCell ref="O9:AN9"/>
-    <mergeCell ref="O10:AN10"/>
-    <mergeCell ref="S12:AJ12"/>
-    <mergeCell ref="S13:AJ13"/>
+    <mergeCell ref="U21:Y24"/>
+    <mergeCell ref="Z21:AD24"/>
+    <mergeCell ref="AE21:AI24"/>
+    <mergeCell ref="S33:AJ33"/>
+    <mergeCell ref="S34:AJ35"/>
     <mergeCell ref="AA15:AF15"/>
     <mergeCell ref="AA17:AF17"/>
     <mergeCell ref="AA19:AF19"/>
     <mergeCell ref="U20:Y20"/>
     <mergeCell ref="Z20:AD20"/>
     <mergeCell ref="AE20:AI20"/>
-    <mergeCell ref="U21:Y24"/>
-    <mergeCell ref="Z21:AD24"/>
-    <mergeCell ref="AE21:AI24"/>
-    <mergeCell ref="S33:AJ33"/>
-    <mergeCell ref="S34:AJ35"/>
+    <mergeCell ref="O8:AN8"/>
+    <mergeCell ref="O9:AN9"/>
+    <mergeCell ref="O10:AN10"/>
+    <mergeCell ref="S12:AJ12"/>
+    <mergeCell ref="S13:AJ13"/>
   </mergeCells>
   <phoneticPr fontId="32"/>
   <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="1.0291666666666699" bottom="1.07083333333333" header="0.31527777777777799" footer="0.31527777777777799"/>
@@ -13476,206 +13243,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="66" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="67" t="str">
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="60" t="str">
         <f>表紙!S12</f>
         <v>エビデンス　画面レイアウト設計</v>
       </c>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="67"/>
-      <c r="AG1" s="67"/>
-      <c r="AH1" s="67"/>
-      <c r="AI1" s="67"/>
-      <c r="AJ1" s="58" t="s">
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="AK1" s="58"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
-      <c r="AN1" s="58"/>
-      <c r="AO1" s="57" t="s">
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="57"/>
-      <c r="AR1" s="57"/>
-      <c r="AS1" s="57"/>
-      <c r="AT1" s="57" t="s">
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AU1" s="57"/>
-      <c r="AV1" s="57"/>
-      <c r="AW1" s="57"/>
-      <c r="AX1" s="57"/>
-      <c r="AY1" s="58" t="s">
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="AZ1" s="58"/>
-      <c r="BA1" s="58"/>
-      <c r="BB1" s="58"/>
-      <c r="BC1" s="58"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="52"/>
+      <c r="BB1" s="52"/>
+      <c r="BC1" s="52"/>
     </row>
     <row r="2" spans="1:55" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="59" t="str">
+      <c r="A2" s="53" t="str">
         <f>表紙!O10</f>
         <v>体験型Java研修</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60" t="str">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54" t="str">
         <f>表紙!O9</f>
         <v>LMS学習管理システム</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61" t="s">
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="62" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK2" s="62"/>
-      <c r="AL2" s="62"/>
-      <c r="AM2" s="62"/>
-      <c r="AN2" s="62"/>
-      <c r="AO2" s="63">
-        <v>44295</v>
-      </c>
-      <c r="AP2" s="63"/>
-      <c r="AQ2" s="63"/>
-      <c r="AR2" s="63"/>
-      <c r="AS2" s="63"/>
-      <c r="AT2" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU2" s="64"/>
-      <c r="AV2" s="64"/>
-      <c r="AW2" s="64"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="65">
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="58">
         <v>45861</v>
       </c>
-      <c r="AZ2" s="65"/>
-      <c r="BA2" s="65"/>
-      <c r="BB2" s="65"/>
-      <c r="BC2" s="65"/>
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="58"/>
+      <c r="AR2" s="58"/>
+      <c r="AS2" s="58"/>
+      <c r="AT2" s="57"/>
+      <c r="AU2" s="57"/>
+      <c r="AV2" s="57"/>
+      <c r="AW2" s="57"/>
+      <c r="AX2" s="57"/>
+      <c r="AY2" s="58"/>
+      <c r="AZ2" s="58"/>
+      <c r="BA2" s="58"/>
+      <c r="BB2" s="58"/>
+      <c r="BC2" s="58"/>
     </row>
     <row r="3" spans="1:55" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="61"/>
-      <c r="Y3" s="61"/>
-      <c r="Z3" s="61"/>
-      <c r="AA3" s="61"/>
-      <c r="AB3" s="61"/>
-      <c r="AC3" s="61"/>
-      <c r="AD3" s="61"/>
-      <c r="AE3" s="61"/>
-      <c r="AF3" s="61"/>
-      <c r="AG3" s="61"/>
-      <c r="AH3" s="61"/>
-      <c r="AI3" s="61"/>
-      <c r="AJ3" s="62"/>
-      <c r="AK3" s="62"/>
-      <c r="AL3" s="62"/>
-      <c r="AM3" s="62"/>
-      <c r="AN3" s="62"/>
-      <c r="AO3" s="63"/>
-      <c r="AP3" s="63"/>
-      <c r="AQ3" s="63"/>
-      <c r="AR3" s="63"/>
-      <c r="AS3" s="63"/>
-      <c r="AT3" s="64"/>
-      <c r="AU3" s="64"/>
-      <c r="AV3" s="64"/>
-      <c r="AW3" s="64"/>
-      <c r="AX3" s="64"/>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="65"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56"/>
+      <c r="AN3" s="56"/>
+      <c r="AO3" s="58"/>
+      <c r="AP3" s="58"/>
+      <c r="AQ3" s="58"/>
+      <c r="AR3" s="58"/>
+      <c r="AS3" s="58"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="58"/>
+      <c r="AZ3" s="58"/>
+      <c r="BA3" s="58"/>
+      <c r="BB3" s="58"/>
+      <c r="BC3" s="58"/>
     </row>
     <row r="4" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="22"/>
@@ -13707,1576 +13470,1611 @@
       <c r="BC4" s="22"/>
     </row>
     <row r="5" spans="1:55" s="25" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56" t="s">
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56" t="s">
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56" t="s">
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="61"/>
+      <c r="AB5" s="61"/>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="61"/>
+      <c r="AE5" s="61"/>
+      <c r="AF5" s="61"/>
+      <c r="AG5" s="61"/>
+      <c r="AH5" s="61"/>
+      <c r="AI5" s="61"/>
+      <c r="AJ5" s="61"/>
+      <c r="AK5" s="61"/>
+      <c r="AL5" s="61"/>
+      <c r="AM5" s="61"/>
+      <c r="AN5" s="61"/>
+      <c r="AO5" s="61"/>
+      <c r="AP5" s="61"/>
+      <c r="AQ5" s="61"/>
+      <c r="AR5" s="61"/>
+      <c r="AS5" s="61"/>
+      <c r="AT5" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="56"/>
-      <c r="AB5" s="56"/>
-      <c r="AC5" s="56"/>
-      <c r="AD5" s="56"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="56"/>
-      <c r="AG5" s="56"/>
-      <c r="AH5" s="56"/>
-      <c r="AI5" s="56"/>
-      <c r="AJ5" s="56"/>
-      <c r="AK5" s="56"/>
-      <c r="AL5" s="56"/>
-      <c r="AM5" s="56"/>
-      <c r="AN5" s="56"/>
-      <c r="AO5" s="56"/>
-      <c r="AP5" s="56"/>
-      <c r="AQ5" s="56"/>
-      <c r="AR5" s="56"/>
-      <c r="AS5" s="56"/>
-      <c r="AT5" s="56" t="s">
+      <c r="AU5" s="61"/>
+      <c r="AV5" s="61"/>
+      <c r="AW5" s="61"/>
+      <c r="AX5" s="61"/>
+      <c r="AY5" s="61"/>
+      <c r="AZ5" s="61"/>
+      <c r="BA5" s="61"/>
+      <c r="BB5" s="61"/>
+      <c r="BC5" s="61"/>
+    </row>
+    <row r="6" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="61"/>
+      <c r="Z6" s="61"/>
+      <c r="AA6" s="61"/>
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="61"/>
+      <c r="AD6" s="61"/>
+      <c r="AE6" s="61"/>
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="61"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="61"/>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="61"/>
+      <c r="AL6" s="61"/>
+      <c r="AM6" s="61"/>
+      <c r="AN6" s="61"/>
+      <c r="AO6" s="61"/>
+      <c r="AP6" s="61"/>
+      <c r="AQ6" s="61"/>
+      <c r="AR6" s="61"/>
+      <c r="AS6" s="61"/>
+      <c r="AT6" s="61"/>
+      <c r="AU6" s="61"/>
+      <c r="AV6" s="61"/>
+      <c r="AW6" s="61"/>
+      <c r="AX6" s="61"/>
+      <c r="AY6" s="61"/>
+      <c r="AZ6" s="61"/>
+      <c r="BA6" s="61"/>
+      <c r="BB6" s="61"/>
+      <c r="BC6" s="61"/>
+    </row>
+    <row r="7" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="61"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="61"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="61"/>
+      <c r="Y7" s="61"/>
+      <c r="Z7" s="61"/>
+      <c r="AA7" s="61"/>
+      <c r="AB7" s="61"/>
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="61"/>
+      <c r="AM7" s="61"/>
+      <c r="AN7" s="61"/>
+      <c r="AO7" s="61"/>
+      <c r="AP7" s="61"/>
+      <c r="AQ7" s="61"/>
+      <c r="AR7" s="61"/>
+      <c r="AS7" s="61"/>
+      <c r="AT7" s="61"/>
+      <c r="AU7" s="61"/>
+      <c r="AV7" s="61"/>
+      <c r="AW7" s="61"/>
+      <c r="AX7" s="61"/>
+      <c r="AY7" s="61"/>
+      <c r="AZ7" s="61"/>
+      <c r="BA7" s="61"/>
+      <c r="BB7" s="61"/>
+      <c r="BC7" s="61"/>
+    </row>
+    <row r="8" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="62">
+        <v>1</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63">
+        <v>45861</v>
+      </c>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="AU5" s="56"/>
-      <c r="AV5" s="56"/>
-      <c r="AW5" s="56"/>
-      <c r="AX5" s="56"/>
-      <c r="AY5" s="56"/>
-      <c r="AZ5" s="56"/>
-      <c r="BA5" s="56"/>
-      <c r="BB5" s="56"/>
-      <c r="BC5" s="56"/>
-    </row>
-    <row r="6" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="56"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="56"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="56"/>
-      <c r="AE6" s="56"/>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="56"/>
-      <c r="AH6" s="56"/>
-      <c r="AI6" s="56"/>
-      <c r="AJ6" s="56"/>
-      <c r="AK6" s="56"/>
-      <c r="AL6" s="56"/>
-      <c r="AM6" s="56"/>
-      <c r="AN6" s="56"/>
-      <c r="AO6" s="56"/>
-      <c r="AP6" s="56"/>
-      <c r="AQ6" s="56"/>
-      <c r="AR6" s="56"/>
-      <c r="AS6" s="56"/>
-      <c r="AT6" s="56"/>
-      <c r="AU6" s="56"/>
-      <c r="AV6" s="56"/>
-      <c r="AW6" s="56"/>
-      <c r="AX6" s="56"/>
-      <c r="AY6" s="56"/>
-      <c r="AZ6" s="56"/>
-      <c r="BA6" s="56"/>
-      <c r="BB6" s="56"/>
-      <c r="BC6" s="56"/>
-    </row>
-    <row r="7" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="56"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="56"/>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="56"/>
-      <c r="AG7" s="56"/>
-      <c r="AH7" s="56"/>
-      <c r="AI7" s="56"/>
-      <c r="AJ7" s="56"/>
-      <c r="AK7" s="56"/>
-      <c r="AL7" s="56"/>
-      <c r="AM7" s="56"/>
-      <c r="AN7" s="56"/>
-      <c r="AO7" s="56"/>
-      <c r="AP7" s="56"/>
-      <c r="AQ7" s="56"/>
-      <c r="AR7" s="56"/>
-      <c r="AS7" s="56"/>
-      <c r="AT7" s="56"/>
-      <c r="AU7" s="56"/>
-      <c r="AV7" s="56"/>
-      <c r="AW7" s="56"/>
-      <c r="AX7" s="56"/>
-      <c r="AY7" s="56"/>
-      <c r="AZ7" s="56"/>
-      <c r="BA7" s="56"/>
-      <c r="BB7" s="56"/>
-      <c r="BC7" s="56"/>
-    </row>
-    <row r="8" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="52">
-        <v>1</v>
-      </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53">
-        <v>44295</v>
-      </c>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="54" t="s">
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
-      <c r="Z8" s="55"/>
-      <c r="AA8" s="55"/>
-      <c r="AB8" s="55"/>
-      <c r="AC8" s="55"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="55"/>
-      <c r="AG8" s="55"/>
-      <c r="AH8" s="55"/>
-      <c r="AI8" s="55"/>
-      <c r="AJ8" s="55"/>
-      <c r="AK8" s="55"/>
-      <c r="AL8" s="55"/>
-      <c r="AM8" s="55"/>
-      <c r="AN8" s="55"/>
-      <c r="AO8" s="55"/>
-      <c r="AP8" s="55"/>
-      <c r="AQ8" s="55"/>
-      <c r="AR8" s="55"/>
-      <c r="AS8" s="55"/>
-      <c r="AT8" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU8" s="54"/>
-      <c r="AV8" s="54"/>
-      <c r="AW8" s="54"/>
-      <c r="AX8" s="54"/>
-      <c r="AY8" s="54"/>
-      <c r="AZ8" s="54"/>
-      <c r="BA8" s="54"/>
-      <c r="BB8" s="54"/>
-      <c r="BC8" s="54"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="65"/>
+      <c r="AF8" s="65"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
+      <c r="AL8" s="65"/>
+      <c r="AM8" s="65"/>
+      <c r="AN8" s="65"/>
+      <c r="AO8" s="65"/>
+      <c r="AP8" s="65"/>
+      <c r="AQ8" s="65"/>
+      <c r="AR8" s="65"/>
+      <c r="AS8" s="65"/>
+      <c r="AT8" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU8" s="64"/>
+      <c r="AV8" s="64"/>
+      <c r="AW8" s="64"/>
+      <c r="AX8" s="64"/>
+      <c r="AY8" s="64"/>
+      <c r="AZ8" s="64"/>
+      <c r="BA8" s="64"/>
+      <c r="BB8" s="64"/>
+      <c r="BC8" s="64"/>
     </row>
     <row r="9" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="52"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="55"/>
-      <c r="AC9" s="55"/>
-      <c r="AD9" s="55"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="55"/>
-      <c r="AH9" s="55"/>
-      <c r="AI9" s="55"/>
-      <c r="AJ9" s="55"/>
-      <c r="AK9" s="55"/>
-      <c r="AL9" s="55"/>
-      <c r="AM9" s="55"/>
-      <c r="AN9" s="55"/>
-      <c r="AO9" s="55"/>
-      <c r="AP9" s="55"/>
-      <c r="AQ9" s="55"/>
-      <c r="AR9" s="55"/>
-      <c r="AS9" s="55"/>
-      <c r="AT9" s="54"/>
-      <c r="AU9" s="54"/>
-      <c r="AV9" s="54"/>
-      <c r="AW9" s="54"/>
-      <c r="AX9" s="54"/>
-      <c r="AY9" s="54"/>
-      <c r="AZ9" s="54"/>
-      <c r="BA9" s="54"/>
-      <c r="BB9" s="54"/>
-      <c r="BC9" s="54"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="65"/>
+      <c r="AF9" s="65"/>
+      <c r="AG9" s="65"/>
+      <c r="AH9" s="65"/>
+      <c r="AI9" s="65"/>
+      <c r="AJ9" s="65"/>
+      <c r="AK9" s="65"/>
+      <c r="AL9" s="65"/>
+      <c r="AM9" s="65"/>
+      <c r="AN9" s="65"/>
+      <c r="AO9" s="65"/>
+      <c r="AP9" s="65"/>
+      <c r="AQ9" s="65"/>
+      <c r="AR9" s="65"/>
+      <c r="AS9" s="65"/>
+      <c r="AT9" s="64"/>
+      <c r="AU9" s="64"/>
+      <c r="AV9" s="64"/>
+      <c r="AW9" s="64"/>
+      <c r="AX9" s="64"/>
+      <c r="AY9" s="64"/>
+      <c r="AZ9" s="64"/>
+      <c r="BA9" s="64"/>
+      <c r="BB9" s="64"/>
+      <c r="BC9" s="64"/>
     </row>
     <row r="10" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="55"/>
-      <c r="Y10" s="55"/>
-      <c r="Z10" s="55"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="55"/>
-      <c r="AC10" s="55"/>
-      <c r="AD10" s="55"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="55"/>
-      <c r="AG10" s="55"/>
-      <c r="AH10" s="55"/>
-      <c r="AI10" s="55"/>
-      <c r="AJ10" s="55"/>
-      <c r="AK10" s="55"/>
-      <c r="AL10" s="55"/>
-      <c r="AM10" s="55"/>
-      <c r="AN10" s="55"/>
-      <c r="AO10" s="55"/>
-      <c r="AP10" s="55"/>
-      <c r="AQ10" s="55"/>
-      <c r="AR10" s="55"/>
-      <c r="AS10" s="55"/>
-      <c r="AT10" s="54"/>
-      <c r="AU10" s="54"/>
-      <c r="AV10" s="54"/>
-      <c r="AW10" s="54"/>
-      <c r="AX10" s="54"/>
-      <c r="AY10" s="54"/>
-      <c r="AZ10" s="54"/>
-      <c r="BA10" s="54"/>
-      <c r="BB10" s="54"/>
-      <c r="BC10" s="54"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
+      <c r="AE10" s="65"/>
+      <c r="AF10" s="65"/>
+      <c r="AG10" s="65"/>
+      <c r="AH10" s="65"/>
+      <c r="AI10" s="65"/>
+      <c r="AJ10" s="65"/>
+      <c r="AK10" s="65"/>
+      <c r="AL10" s="65"/>
+      <c r="AM10" s="65"/>
+      <c r="AN10" s="65"/>
+      <c r="AO10" s="65"/>
+      <c r="AP10" s="65"/>
+      <c r="AQ10" s="65"/>
+      <c r="AR10" s="65"/>
+      <c r="AS10" s="65"/>
+      <c r="AT10" s="64"/>
+      <c r="AU10" s="64"/>
+      <c r="AV10" s="64"/>
+      <c r="AW10" s="64"/>
+      <c r="AX10" s="64"/>
+      <c r="AY10" s="64"/>
+      <c r="AZ10" s="64"/>
+      <c r="BA10" s="64"/>
+      <c r="BB10" s="64"/>
+      <c r="BC10" s="64"/>
     </row>
     <row r="11" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="52">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53">
-        <v>45861</v>
-      </c>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="69" t="s">
-        <v>118</v>
-      </c>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="55"/>
-      <c r="AB11" s="55"/>
-      <c r="AC11" s="55"/>
-      <c r="AD11" s="55"/>
-      <c r="AE11" s="55"/>
-      <c r="AF11" s="55"/>
-      <c r="AG11" s="55"/>
-      <c r="AH11" s="55"/>
-      <c r="AI11" s="55"/>
-      <c r="AJ11" s="55"/>
-      <c r="AK11" s="55"/>
-      <c r="AL11" s="55"/>
-      <c r="AM11" s="55"/>
-      <c r="AN11" s="55"/>
-      <c r="AO11" s="55"/>
-      <c r="AP11" s="55"/>
-      <c r="AQ11" s="55"/>
-      <c r="AR11" s="55"/>
-      <c r="AS11" s="55"/>
-      <c r="AT11" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="54"/>
-      <c r="AW11" s="54"/>
-      <c r="AX11" s="54"/>
-      <c r="AY11" s="54"/>
-      <c r="AZ11" s="54"/>
-      <c r="BA11" s="54"/>
-      <c r="BB11" s="54"/>
-      <c r="BC11" s="54"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="65"/>
+      <c r="AF11" s="65"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="65"/>
+      <c r="AI11" s="65"/>
+      <c r="AJ11" s="65"/>
+      <c r="AK11" s="65"/>
+      <c r="AL11" s="65"/>
+      <c r="AM11" s="65"/>
+      <c r="AN11" s="65"/>
+      <c r="AO11" s="65"/>
+      <c r="AP11" s="65"/>
+      <c r="AQ11" s="65"/>
+      <c r="AR11" s="65"/>
+      <c r="AS11" s="65"/>
+      <c r="AT11" s="64"/>
+      <c r="AU11" s="64"/>
+      <c r="AV11" s="64"/>
+      <c r="AW11" s="64"/>
+      <c r="AX11" s="64"/>
+      <c r="AY11" s="64"/>
+      <c r="AZ11" s="64"/>
+      <c r="BA11" s="64"/>
+      <c r="BB11" s="64"/>
+      <c r="BC11" s="64"/>
     </row>
     <row r="12" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
-      <c r="Z12" s="55"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="55"/>
-      <c r="AC12" s="55"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="55"/>
-      <c r="AF12" s="55"/>
-      <c r="AG12" s="55"/>
-      <c r="AH12" s="55"/>
-      <c r="AI12" s="55"/>
-      <c r="AJ12" s="55"/>
-      <c r="AK12" s="55"/>
-      <c r="AL12" s="55"/>
-      <c r="AM12" s="55"/>
-      <c r="AN12" s="55"/>
-      <c r="AO12" s="55"/>
-      <c r="AP12" s="55"/>
-      <c r="AQ12" s="55"/>
-      <c r="AR12" s="55"/>
-      <c r="AS12" s="55"/>
-      <c r="AT12" s="54"/>
-      <c r="AU12" s="54"/>
-      <c r="AV12" s="54"/>
-      <c r="AW12" s="54"/>
-      <c r="AX12" s="54"/>
-      <c r="AY12" s="54"/>
-      <c r="AZ12" s="54"/>
-      <c r="BA12" s="54"/>
-      <c r="BB12" s="54"/>
-      <c r="BC12" s="54"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="65"/>
+      <c r="AF12" s="65"/>
+      <c r="AG12" s="65"/>
+      <c r="AH12" s="65"/>
+      <c r="AI12" s="65"/>
+      <c r="AJ12" s="65"/>
+      <c r="AK12" s="65"/>
+      <c r="AL12" s="65"/>
+      <c r="AM12" s="65"/>
+      <c r="AN12" s="65"/>
+      <c r="AO12" s="65"/>
+      <c r="AP12" s="65"/>
+      <c r="AQ12" s="65"/>
+      <c r="AR12" s="65"/>
+      <c r="AS12" s="65"/>
+      <c r="AT12" s="64"/>
+      <c r="AU12" s="64"/>
+      <c r="AV12" s="64"/>
+      <c r="AW12" s="64"/>
+      <c r="AX12" s="64"/>
+      <c r="AY12" s="64"/>
+      <c r="AZ12" s="64"/>
+      <c r="BA12" s="64"/>
+      <c r="BB12" s="64"/>
+      <c r="BC12" s="64"/>
     </row>
     <row r="13" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
-      <c r="Z13" s="55"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="55"/>
-      <c r="AC13" s="55"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="55"/>
-      <c r="AF13" s="55"/>
-      <c r="AG13" s="55"/>
-      <c r="AH13" s="55"/>
-      <c r="AI13" s="55"/>
-      <c r="AJ13" s="55"/>
-      <c r="AK13" s="55"/>
-      <c r="AL13" s="55"/>
-      <c r="AM13" s="55"/>
-      <c r="AN13" s="55"/>
-      <c r="AO13" s="55"/>
-      <c r="AP13" s="55"/>
-      <c r="AQ13" s="55"/>
-      <c r="AR13" s="55"/>
-      <c r="AS13" s="55"/>
-      <c r="AT13" s="54"/>
-      <c r="AU13" s="54"/>
-      <c r="AV13" s="54"/>
-      <c r="AW13" s="54"/>
-      <c r="AX13" s="54"/>
-      <c r="AY13" s="54"/>
-      <c r="AZ13" s="54"/>
-      <c r="BA13" s="54"/>
-      <c r="BB13" s="54"/>
-      <c r="BC13" s="54"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="65"/>
+      <c r="AF13" s="65"/>
+      <c r="AG13" s="65"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="65"/>
+      <c r="AJ13" s="65"/>
+      <c r="AK13" s="65"/>
+      <c r="AL13" s="65"/>
+      <c r="AM13" s="65"/>
+      <c r="AN13" s="65"/>
+      <c r="AO13" s="65"/>
+      <c r="AP13" s="65"/>
+      <c r="AQ13" s="65"/>
+      <c r="AR13" s="65"/>
+      <c r="AS13" s="65"/>
+      <c r="AT13" s="64"/>
+      <c r="AU13" s="64"/>
+      <c r="AV13" s="64"/>
+      <c r="AW13" s="64"/>
+      <c r="AX13" s="64"/>
+      <c r="AY13" s="64"/>
+      <c r="AZ13" s="64"/>
+      <c r="BA13" s="64"/>
+      <c r="BB13" s="64"/>
+      <c r="BC13" s="64"/>
     </row>
     <row r="14" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="51"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
-      <c r="Y14" s="51"/>
-      <c r="Z14" s="51"/>
-      <c r="AA14" s="51"/>
-      <c r="AB14" s="51"/>
-      <c r="AC14" s="51"/>
-      <c r="AD14" s="51"/>
-      <c r="AE14" s="51"/>
-      <c r="AF14" s="51"/>
-      <c r="AG14" s="51"/>
-      <c r="AH14" s="51"/>
-      <c r="AI14" s="51"/>
-      <c r="AJ14" s="51"/>
-      <c r="AK14" s="51"/>
-      <c r="AL14" s="51"/>
-      <c r="AM14" s="51"/>
-      <c r="AN14" s="51"/>
-      <c r="AO14" s="51"/>
-      <c r="AP14" s="51"/>
-      <c r="AQ14" s="51"/>
-      <c r="AR14" s="51"/>
-      <c r="AS14" s="51"/>
-      <c r="AT14" s="51"/>
-      <c r="AU14" s="51"/>
-      <c r="AV14" s="51"/>
-      <c r="AW14" s="51"/>
-      <c r="AX14" s="51"/>
-      <c r="AY14" s="51"/>
-      <c r="AZ14" s="51"/>
-      <c r="BA14" s="51"/>
-      <c r="BB14" s="51"/>
-      <c r="BC14" s="51"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="67"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="67"/>
+      <c r="AC14" s="67"/>
+      <c r="AD14" s="67"/>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="67"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
+      <c r="AL14" s="67"/>
+      <c r="AM14" s="67"/>
+      <c r="AN14" s="67"/>
+      <c r="AO14" s="67"/>
+      <c r="AP14" s="67"/>
+      <c r="AQ14" s="67"/>
+      <c r="AR14" s="67"/>
+      <c r="AS14" s="67"/>
+      <c r="AT14" s="67"/>
+      <c r="AU14" s="67"/>
+      <c r="AV14" s="67"/>
+      <c r="AW14" s="67"/>
+      <c r="AX14" s="67"/>
+      <c r="AY14" s="67"/>
+      <c r="AZ14" s="67"/>
+      <c r="BA14" s="67"/>
+      <c r="BB14" s="67"/>
+      <c r="BC14" s="67"/>
     </row>
     <row r="15" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="51"/>
-      <c r="V15" s="51"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
-      <c r="Z15" s="51"/>
-      <c r="AA15" s="51"/>
-      <c r="AB15" s="51"/>
-      <c r="AC15" s="51"/>
-      <c r="AD15" s="51"/>
-      <c r="AE15" s="51"/>
-      <c r="AF15" s="51"/>
-      <c r="AG15" s="51"/>
-      <c r="AH15" s="51"/>
-      <c r="AI15" s="51"/>
-      <c r="AJ15" s="51"/>
-      <c r="AK15" s="51"/>
-      <c r="AL15" s="51"/>
-      <c r="AM15" s="51"/>
-      <c r="AN15" s="51"/>
-      <c r="AO15" s="51"/>
-      <c r="AP15" s="51"/>
-      <c r="AQ15" s="51"/>
-      <c r="AR15" s="51"/>
-      <c r="AS15" s="51"/>
-      <c r="AT15" s="51"/>
-      <c r="AU15" s="51"/>
-      <c r="AV15" s="51"/>
-      <c r="AW15" s="51"/>
-      <c r="AX15" s="51"/>
-      <c r="AY15" s="51"/>
-      <c r="AZ15" s="51"/>
-      <c r="BA15" s="51"/>
-      <c r="BB15" s="51"/>
-      <c r="BC15" s="51"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="67"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="67"/>
+      <c r="AN15" s="67"/>
+      <c r="AO15" s="67"/>
+      <c r="AP15" s="67"/>
+      <c r="AQ15" s="67"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="67"/>
+      <c r="AT15" s="67"/>
+      <c r="AU15" s="67"/>
+      <c r="AV15" s="67"/>
+      <c r="AW15" s="67"/>
+      <c r="AX15" s="67"/>
+      <c r="AY15" s="67"/>
+      <c r="AZ15" s="67"/>
+      <c r="BA15" s="67"/>
+      <c r="BB15" s="67"/>
+      <c r="BC15" s="67"/>
     </row>
     <row r="16" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="51"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="51"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="51"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="51"/>
-      <c r="AC16" s="51"/>
-      <c r="AD16" s="51"/>
-      <c r="AE16" s="51"/>
-      <c r="AF16" s="51"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="51"/>
-      <c r="AI16" s="51"/>
-      <c r="AJ16" s="51"/>
-      <c r="AK16" s="51"/>
-      <c r="AL16" s="51"/>
-      <c r="AM16" s="51"/>
-      <c r="AN16" s="51"/>
-      <c r="AO16" s="51"/>
-      <c r="AP16" s="51"/>
-      <c r="AQ16" s="51"/>
-      <c r="AR16" s="51"/>
-      <c r="AS16" s="51"/>
-      <c r="AT16" s="51"/>
-      <c r="AU16" s="51"/>
-      <c r="AV16" s="51"/>
-      <c r="AW16" s="51"/>
-      <c r="AX16" s="51"/>
-      <c r="AY16" s="51"/>
-      <c r="AZ16" s="51"/>
-      <c r="BA16" s="51"/>
-      <c r="BB16" s="51"/>
-      <c r="BC16" s="51"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
+      <c r="AL16" s="67"/>
+      <c r="AM16" s="67"/>
+      <c r="AN16" s="67"/>
+      <c r="AO16" s="67"/>
+      <c r="AP16" s="67"/>
+      <c r="AQ16" s="67"/>
+      <c r="AR16" s="67"/>
+      <c r="AS16" s="67"/>
+      <c r="AT16" s="67"/>
+      <c r="AU16" s="67"/>
+      <c r="AV16" s="67"/>
+      <c r="AW16" s="67"/>
+      <c r="AX16" s="67"/>
+      <c r="AY16" s="67"/>
+      <c r="AZ16" s="67"/>
+      <c r="BA16" s="67"/>
+      <c r="BB16" s="67"/>
+      <c r="BC16" s="67"/>
     </row>
     <row r="17" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="51"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="51"/>
-      <c r="U17" s="51"/>
-      <c r="V17" s="51"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
-      <c r="Y17" s="51"/>
-      <c r="Z17" s="51"/>
-      <c r="AA17" s="51"/>
-      <c r="AB17" s="51"/>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
-      <c r="AE17" s="51"/>
-      <c r="AF17" s="51"/>
-      <c r="AG17" s="51"/>
-      <c r="AH17" s="51"/>
-      <c r="AI17" s="51"/>
-      <c r="AJ17" s="51"/>
-      <c r="AK17" s="51"/>
-      <c r="AL17" s="51"/>
-      <c r="AM17" s="51"/>
-      <c r="AN17" s="51"/>
-      <c r="AO17" s="51"/>
-      <c r="AP17" s="51"/>
-      <c r="AQ17" s="51"/>
-      <c r="AR17" s="51"/>
-      <c r="AS17" s="51"/>
-      <c r="AT17" s="51"/>
-      <c r="AU17" s="51"/>
-      <c r="AV17" s="51"/>
-      <c r="AW17" s="51"/>
-      <c r="AX17" s="51"/>
-      <c r="AY17" s="51"/>
-      <c r="AZ17" s="51"/>
-      <c r="BA17" s="51"/>
-      <c r="BB17" s="51"/>
-      <c r="BC17" s="51"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
+      <c r="AL17" s="67"/>
+      <c r="AM17" s="67"/>
+      <c r="AN17" s="67"/>
+      <c r="AO17" s="67"/>
+      <c r="AP17" s="67"/>
+      <c r="AQ17" s="67"/>
+      <c r="AR17" s="67"/>
+      <c r="AS17" s="67"/>
+      <c r="AT17" s="67"/>
+      <c r="AU17" s="67"/>
+      <c r="AV17" s="67"/>
+      <c r="AW17" s="67"/>
+      <c r="AX17" s="67"/>
+      <c r="AY17" s="67"/>
+      <c r="AZ17" s="67"/>
+      <c r="BA17" s="67"/>
+      <c r="BB17" s="67"/>
+      <c r="BC17" s="67"/>
     </row>
     <row r="18" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="51"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="51"/>
-      <c r="Z18" s="51"/>
-      <c r="AA18" s="51"/>
-      <c r="AB18" s="51"/>
-      <c r="AC18" s="51"/>
-      <c r="AD18" s="51"/>
-      <c r="AE18" s="51"/>
-      <c r="AF18" s="51"/>
-      <c r="AG18" s="51"/>
-      <c r="AH18" s="51"/>
-      <c r="AI18" s="51"/>
-      <c r="AJ18" s="51"/>
-      <c r="AK18" s="51"/>
-      <c r="AL18" s="51"/>
-      <c r="AM18" s="51"/>
-      <c r="AN18" s="51"/>
-      <c r="AO18" s="51"/>
-      <c r="AP18" s="51"/>
-      <c r="AQ18" s="51"/>
-      <c r="AR18" s="51"/>
-      <c r="AS18" s="51"/>
-      <c r="AT18" s="51"/>
-      <c r="AU18" s="51"/>
-      <c r="AV18" s="51"/>
-      <c r="AW18" s="51"/>
-      <c r="AX18" s="51"/>
-      <c r="AY18" s="51"/>
-      <c r="AZ18" s="51"/>
-      <c r="BA18" s="51"/>
-      <c r="BB18" s="51"/>
-      <c r="BC18" s="51"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
+      <c r="AL18" s="67"/>
+      <c r="AM18" s="67"/>
+      <c r="AN18" s="67"/>
+      <c r="AO18" s="67"/>
+      <c r="AP18" s="67"/>
+      <c r="AQ18" s="67"/>
+      <c r="AR18" s="67"/>
+      <c r="AS18" s="67"/>
+      <c r="AT18" s="67"/>
+      <c r="AU18" s="67"/>
+      <c r="AV18" s="67"/>
+      <c r="AW18" s="67"/>
+      <c r="AX18" s="67"/>
+      <c r="AY18" s="67"/>
+      <c r="AZ18" s="67"/>
+      <c r="BA18" s="67"/>
+      <c r="BB18" s="67"/>
+      <c r="BC18" s="67"/>
     </row>
     <row r="19" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="51"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="51"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="51"/>
-      <c r="V19" s="51"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="51"/>
-      <c r="Y19" s="51"/>
-      <c r="Z19" s="51"/>
-      <c r="AA19" s="51"/>
-      <c r="AB19" s="51"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="51"/>
-      <c r="AE19" s="51"/>
-      <c r="AF19" s="51"/>
-      <c r="AG19" s="51"/>
-      <c r="AH19" s="51"/>
-      <c r="AI19" s="51"/>
-      <c r="AJ19" s="51"/>
-      <c r="AK19" s="51"/>
-      <c r="AL19" s="51"/>
-      <c r="AM19" s="51"/>
-      <c r="AN19" s="51"/>
-      <c r="AO19" s="51"/>
-      <c r="AP19" s="51"/>
-      <c r="AQ19" s="51"/>
-      <c r="AR19" s="51"/>
-      <c r="AS19" s="51"/>
-      <c r="AT19" s="51"/>
-      <c r="AU19" s="51"/>
-      <c r="AV19" s="51"/>
-      <c r="AW19" s="51"/>
-      <c r="AX19" s="51"/>
-      <c r="AY19" s="51"/>
-      <c r="AZ19" s="51"/>
-      <c r="BA19" s="51"/>
-      <c r="BB19" s="51"/>
-      <c r="BC19" s="51"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="67"/>
+      <c r="AA19" s="67"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="67"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="67"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
+      <c r="AK19" s="67"/>
+      <c r="AL19" s="67"/>
+      <c r="AM19" s="67"/>
+      <c r="AN19" s="67"/>
+      <c r="AO19" s="67"/>
+      <c r="AP19" s="67"/>
+      <c r="AQ19" s="67"/>
+      <c r="AR19" s="67"/>
+      <c r="AS19" s="67"/>
+      <c r="AT19" s="67"/>
+      <c r="AU19" s="67"/>
+      <c r="AV19" s="67"/>
+      <c r="AW19" s="67"/>
+      <c r="AX19" s="67"/>
+      <c r="AY19" s="67"/>
+      <c r="AZ19" s="67"/>
+      <c r="BA19" s="67"/>
+      <c r="BB19" s="67"/>
+      <c r="BC19" s="67"/>
     </row>
     <row r="20" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="51"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="51"/>
-      <c r="Y20" s="51"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="51"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="51"/>
-      <c r="AE20" s="51"/>
-      <c r="AF20" s="51"/>
-      <c r="AG20" s="51"/>
-      <c r="AH20" s="51"/>
-      <c r="AI20" s="51"/>
-      <c r="AJ20" s="51"/>
-      <c r="AK20" s="51"/>
-      <c r="AL20" s="51"/>
-      <c r="AM20" s="51"/>
-      <c r="AN20" s="51"/>
-      <c r="AO20" s="51"/>
-      <c r="AP20" s="51"/>
-      <c r="AQ20" s="51"/>
-      <c r="AR20" s="51"/>
-      <c r="AS20" s="51"/>
-      <c r="AT20" s="51"/>
-      <c r="AU20" s="51"/>
-      <c r="AV20" s="51"/>
-      <c r="AW20" s="51"/>
-      <c r="AX20" s="51"/>
-      <c r="AY20" s="51"/>
-      <c r="AZ20" s="51"/>
-      <c r="BA20" s="51"/>
-      <c r="BB20" s="51"/>
-      <c r="BC20" s="51"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="67"/>
+      <c r="AN20" s="67"/>
+      <c r="AO20" s="67"/>
+      <c r="AP20" s="67"/>
+      <c r="AQ20" s="67"/>
+      <c r="AR20" s="67"/>
+      <c r="AS20" s="67"/>
+      <c r="AT20" s="67"/>
+      <c r="AU20" s="67"/>
+      <c r="AV20" s="67"/>
+      <c r="AW20" s="67"/>
+      <c r="AX20" s="67"/>
+      <c r="AY20" s="67"/>
+      <c r="AZ20" s="67"/>
+      <c r="BA20" s="67"/>
+      <c r="BB20" s="67"/>
+      <c r="BC20" s="67"/>
     </row>
     <row r="21" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="51"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="51"/>
-      <c r="Z21" s="51"/>
-      <c r="AA21" s="51"/>
-      <c r="AB21" s="51"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="51"/>
-      <c r="AE21" s="51"/>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="51"/>
-      <c r="AH21" s="51"/>
-      <c r="AI21" s="51"/>
-      <c r="AJ21" s="51"/>
-      <c r="AK21" s="51"/>
-      <c r="AL21" s="51"/>
-      <c r="AM21" s="51"/>
-      <c r="AN21" s="51"/>
-      <c r="AO21" s="51"/>
-      <c r="AP21" s="51"/>
-      <c r="AQ21" s="51"/>
-      <c r="AR21" s="51"/>
-      <c r="AS21" s="51"/>
-      <c r="AT21" s="51"/>
-      <c r="AU21" s="51"/>
-      <c r="AV21" s="51"/>
-      <c r="AW21" s="51"/>
-      <c r="AX21" s="51"/>
-      <c r="AY21" s="51"/>
-      <c r="AZ21" s="51"/>
-      <c r="BA21" s="51"/>
-      <c r="BB21" s="51"/>
-      <c r="BC21" s="51"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="67"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
+      <c r="AL21" s="67"/>
+      <c r="AM21" s="67"/>
+      <c r="AN21" s="67"/>
+      <c r="AO21" s="67"/>
+      <c r="AP21" s="67"/>
+      <c r="AQ21" s="67"/>
+      <c r="AR21" s="67"/>
+      <c r="AS21" s="67"/>
+      <c r="AT21" s="67"/>
+      <c r="AU21" s="67"/>
+      <c r="AV21" s="67"/>
+      <c r="AW21" s="67"/>
+      <c r="AX21" s="67"/>
+      <c r="AY21" s="67"/>
+      <c r="AZ21" s="67"/>
+      <c r="BA21" s="67"/>
+      <c r="BB21" s="67"/>
+      <c r="BC21" s="67"/>
     </row>
     <row r="22" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="51"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="51"/>
-      <c r="X22" s="51"/>
-      <c r="Y22" s="51"/>
-      <c r="Z22" s="51"/>
-      <c r="AA22" s="51"/>
-      <c r="AB22" s="51"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="51"/>
-      <c r="AE22" s="51"/>
-      <c r="AF22" s="51"/>
-      <c r="AG22" s="51"/>
-      <c r="AH22" s="51"/>
-      <c r="AI22" s="51"/>
-      <c r="AJ22" s="51"/>
-      <c r="AK22" s="51"/>
-      <c r="AL22" s="51"/>
-      <c r="AM22" s="51"/>
-      <c r="AN22" s="51"/>
-      <c r="AO22" s="51"/>
-      <c r="AP22" s="51"/>
-      <c r="AQ22" s="51"/>
-      <c r="AR22" s="51"/>
-      <c r="AS22" s="51"/>
-      <c r="AT22" s="51"/>
-      <c r="AU22" s="51"/>
-      <c r="AV22" s="51"/>
-      <c r="AW22" s="51"/>
-      <c r="AX22" s="51"/>
-      <c r="AY22" s="51"/>
-      <c r="AZ22" s="51"/>
-      <c r="BA22" s="51"/>
-      <c r="BB22" s="51"/>
-      <c r="BC22" s="51"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
+      <c r="AL22" s="67"/>
+      <c r="AM22" s="67"/>
+      <c r="AN22" s="67"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="67"/>
+      <c r="AQ22" s="67"/>
+      <c r="AR22" s="67"/>
+      <c r="AS22" s="67"/>
+      <c r="AT22" s="67"/>
+      <c r="AU22" s="67"/>
+      <c r="AV22" s="67"/>
+      <c r="AW22" s="67"/>
+      <c r="AX22" s="67"/>
+      <c r="AY22" s="67"/>
+      <c r="AZ22" s="67"/>
+      <c r="BA22" s="67"/>
+      <c r="BB22" s="67"/>
+      <c r="BC22" s="67"/>
     </row>
     <row r="23" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="51"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="51"/>
-      <c r="V23" s="51"/>
-      <c r="W23" s="51"/>
-      <c r="X23" s="51"/>
-      <c r="Y23" s="51"/>
-      <c r="Z23" s="51"/>
-      <c r="AA23" s="51"/>
-      <c r="AB23" s="51"/>
-      <c r="AC23" s="51"/>
-      <c r="AD23" s="51"/>
-      <c r="AE23" s="51"/>
-      <c r="AF23" s="51"/>
-      <c r="AG23" s="51"/>
-      <c r="AH23" s="51"/>
-      <c r="AI23" s="51"/>
-      <c r="AJ23" s="51"/>
-      <c r="AK23" s="51"/>
-      <c r="AL23" s="51"/>
-      <c r="AM23" s="51"/>
-      <c r="AN23" s="51"/>
-      <c r="AO23" s="51"/>
-      <c r="AP23" s="51"/>
-      <c r="AQ23" s="51"/>
-      <c r="AR23" s="51"/>
-      <c r="AS23" s="51"/>
-      <c r="AT23" s="51"/>
-      <c r="AU23" s="51"/>
-      <c r="AV23" s="51"/>
-      <c r="AW23" s="51"/>
-      <c r="AX23" s="51"/>
-      <c r="AY23" s="51"/>
-      <c r="AZ23" s="51"/>
-      <c r="BA23" s="51"/>
-      <c r="BB23" s="51"/>
-      <c r="BC23" s="51"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="67"/>
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="67"/>
+      <c r="AQ23" s="67"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="67"/>
+      <c r="AT23" s="67"/>
+      <c r="AU23" s="67"/>
+      <c r="AV23" s="67"/>
+      <c r="AW23" s="67"/>
+      <c r="AX23" s="67"/>
+      <c r="AY23" s="67"/>
+      <c r="AZ23" s="67"/>
+      <c r="BA23" s="67"/>
+      <c r="BB23" s="67"/>
+      <c r="BC23" s="67"/>
     </row>
     <row r="24" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="51"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="51"/>
-      <c r="Y24" s="51"/>
-      <c r="Z24" s="51"/>
-      <c r="AA24" s="51"/>
-      <c r="AB24" s="51"/>
-      <c r="AC24" s="51"/>
-      <c r="AD24" s="51"/>
-      <c r="AE24" s="51"/>
-      <c r="AF24" s="51"/>
-      <c r="AG24" s="51"/>
-      <c r="AH24" s="51"/>
-      <c r="AI24" s="51"/>
-      <c r="AJ24" s="51"/>
-      <c r="AK24" s="51"/>
-      <c r="AL24" s="51"/>
-      <c r="AM24" s="51"/>
-      <c r="AN24" s="51"/>
-      <c r="AO24" s="51"/>
-      <c r="AP24" s="51"/>
-      <c r="AQ24" s="51"/>
-      <c r="AR24" s="51"/>
-      <c r="AS24" s="51"/>
-      <c r="AT24" s="51"/>
-      <c r="AU24" s="51"/>
-      <c r="AV24" s="51"/>
-      <c r="AW24" s="51"/>
-      <c r="AX24" s="51"/>
-      <c r="AY24" s="51"/>
-      <c r="AZ24" s="51"/>
-      <c r="BA24" s="51"/>
-      <c r="BB24" s="51"/>
-      <c r="BC24" s="51"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="67"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
+      <c r="AL24" s="67"/>
+      <c r="AM24" s="67"/>
+      <c r="AN24" s="67"/>
+      <c r="AO24" s="67"/>
+      <c r="AP24" s="67"/>
+      <c r="AQ24" s="67"/>
+      <c r="AR24" s="67"/>
+      <c r="AS24" s="67"/>
+      <c r="AT24" s="67"/>
+      <c r="AU24" s="67"/>
+      <c r="AV24" s="67"/>
+      <c r="AW24" s="67"/>
+      <c r="AX24" s="67"/>
+      <c r="AY24" s="67"/>
+      <c r="AZ24" s="67"/>
+      <c r="BA24" s="67"/>
+      <c r="BB24" s="67"/>
+      <c r="BC24" s="67"/>
     </row>
     <row r="25" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="51"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="51"/>
-      <c r="S25" s="51"/>
-      <c r="T25" s="51"/>
-      <c r="U25" s="51"/>
-      <c r="V25" s="51"/>
-      <c r="W25" s="51"/>
-      <c r="X25" s="51"/>
-      <c r="Y25" s="51"/>
-      <c r="Z25" s="51"/>
-      <c r="AA25" s="51"/>
-      <c r="AB25" s="51"/>
-      <c r="AC25" s="51"/>
-      <c r="AD25" s="51"/>
-      <c r="AE25" s="51"/>
-      <c r="AF25" s="51"/>
-      <c r="AG25" s="51"/>
-      <c r="AH25" s="51"/>
-      <c r="AI25" s="51"/>
-      <c r="AJ25" s="51"/>
-      <c r="AK25" s="51"/>
-      <c r="AL25" s="51"/>
-      <c r="AM25" s="51"/>
-      <c r="AN25" s="51"/>
-      <c r="AO25" s="51"/>
-      <c r="AP25" s="51"/>
-      <c r="AQ25" s="51"/>
-      <c r="AR25" s="51"/>
-      <c r="AS25" s="51"/>
-      <c r="AT25" s="51"/>
-      <c r="AU25" s="51"/>
-      <c r="AV25" s="51"/>
-      <c r="AW25" s="51"/>
-      <c r="AX25" s="51"/>
-      <c r="AY25" s="51"/>
-      <c r="AZ25" s="51"/>
-      <c r="BA25" s="51"/>
-      <c r="BB25" s="51"/>
-      <c r="BC25" s="51"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="67"/>
+      <c r="AE25" s="67"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
+      <c r="AL25" s="67"/>
+      <c r="AM25" s="67"/>
+      <c r="AN25" s="67"/>
+      <c r="AO25" s="67"/>
+      <c r="AP25" s="67"/>
+      <c r="AQ25" s="67"/>
+      <c r="AR25" s="67"/>
+      <c r="AS25" s="67"/>
+      <c r="AT25" s="67"/>
+      <c r="AU25" s="67"/>
+      <c r="AV25" s="67"/>
+      <c r="AW25" s="67"/>
+      <c r="AX25" s="67"/>
+      <c r="AY25" s="67"/>
+      <c r="AZ25" s="67"/>
+      <c r="BA25" s="67"/>
+      <c r="BB25" s="67"/>
+      <c r="BC25" s="67"/>
     </row>
     <row r="26" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="51"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="51"/>
-      <c r="AA26" s="51"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="51"/>
-      <c r="AE26" s="51"/>
-      <c r="AF26" s="51"/>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="51"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="51"/>
-      <c r="AL26" s="51"/>
-      <c r="AM26" s="51"/>
-      <c r="AN26" s="51"/>
-      <c r="AO26" s="51"/>
-      <c r="AP26" s="51"/>
-      <c r="AQ26" s="51"/>
-      <c r="AR26" s="51"/>
-      <c r="AS26" s="51"/>
-      <c r="AT26" s="51"/>
-      <c r="AU26" s="51"/>
-      <c r="AV26" s="51"/>
-      <c r="AW26" s="51"/>
-      <c r="AX26" s="51"/>
-      <c r="AY26" s="51"/>
-      <c r="AZ26" s="51"/>
-      <c r="BA26" s="51"/>
-      <c r="BB26" s="51"/>
-      <c r="BC26" s="51"/>
+      <c r="A26" s="67"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
+      <c r="AA26" s="67"/>
+      <c r="AB26" s="67"/>
+      <c r="AC26" s="67"/>
+      <c r="AD26" s="67"/>
+      <c r="AE26" s="67"/>
+      <c r="AF26" s="67"/>
+      <c r="AG26" s="67"/>
+      <c r="AH26" s="67"/>
+      <c r="AI26" s="67"/>
+      <c r="AJ26" s="67"/>
+      <c r="AK26" s="67"/>
+      <c r="AL26" s="67"/>
+      <c r="AM26" s="67"/>
+      <c r="AN26" s="67"/>
+      <c r="AO26" s="67"/>
+      <c r="AP26" s="67"/>
+      <c r="AQ26" s="67"/>
+      <c r="AR26" s="67"/>
+      <c r="AS26" s="67"/>
+      <c r="AT26" s="67"/>
+      <c r="AU26" s="67"/>
+      <c r="AV26" s="67"/>
+      <c r="AW26" s="67"/>
+      <c r="AX26" s="67"/>
+      <c r="AY26" s="67"/>
+      <c r="AZ26" s="67"/>
+      <c r="BA26" s="67"/>
+      <c r="BB26" s="67"/>
+      <c r="BC26" s="67"/>
     </row>
     <row r="27" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="51"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="51"/>
-      <c r="AA27" s="51"/>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="51"/>
-      <c r="AE27" s="51"/>
-      <c r="AF27" s="51"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="51"/>
-      <c r="AK27" s="51"/>
-      <c r="AL27" s="51"/>
-      <c r="AM27" s="51"/>
-      <c r="AN27" s="51"/>
-      <c r="AO27" s="51"/>
-      <c r="AP27" s="51"/>
-      <c r="AQ27" s="51"/>
-      <c r="AR27" s="51"/>
-      <c r="AS27" s="51"/>
-      <c r="AT27" s="51"/>
-      <c r="AU27" s="51"/>
-      <c r="AV27" s="51"/>
-      <c r="AW27" s="51"/>
-      <c r="AX27" s="51"/>
-      <c r="AY27" s="51"/>
-      <c r="AZ27" s="51"/>
-      <c r="BA27" s="51"/>
-      <c r="BB27" s="51"/>
-      <c r="BC27" s="51"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67"/>
+      <c r="Z27" s="67"/>
+      <c r="AA27" s="67"/>
+      <c r="AB27" s="67"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="67"/>
+      <c r="AE27" s="67"/>
+      <c r="AF27" s="67"/>
+      <c r="AG27" s="67"/>
+      <c r="AH27" s="67"/>
+      <c r="AI27" s="67"/>
+      <c r="AJ27" s="67"/>
+      <c r="AK27" s="67"/>
+      <c r="AL27" s="67"/>
+      <c r="AM27" s="67"/>
+      <c r="AN27" s="67"/>
+      <c r="AO27" s="67"/>
+      <c r="AP27" s="67"/>
+      <c r="AQ27" s="67"/>
+      <c r="AR27" s="67"/>
+      <c r="AS27" s="67"/>
+      <c r="AT27" s="67"/>
+      <c r="AU27" s="67"/>
+      <c r="AV27" s="67"/>
+      <c r="AW27" s="67"/>
+      <c r="AX27" s="67"/>
+      <c r="AY27" s="67"/>
+      <c r="AZ27" s="67"/>
+      <c r="BA27" s="67"/>
+      <c r="BB27" s="67"/>
+      <c r="BC27" s="67"/>
     </row>
     <row r="28" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="51"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="51"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
-      <c r="AL28" s="51"/>
-      <c r="AM28" s="51"/>
-      <c r="AN28" s="51"/>
-      <c r="AO28" s="51"/>
-      <c r="AP28" s="51"/>
-      <c r="AQ28" s="51"/>
-      <c r="AR28" s="51"/>
-      <c r="AS28" s="51"/>
-      <c r="AT28" s="51"/>
-      <c r="AU28" s="51"/>
-      <c r="AV28" s="51"/>
-      <c r="AW28" s="51"/>
-      <c r="AX28" s="51"/>
-      <c r="AY28" s="51"/>
-      <c r="AZ28" s="51"/>
-      <c r="BA28" s="51"/>
-      <c r="BB28" s="51"/>
-      <c r="BC28" s="51"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
+      <c r="AA28" s="67"/>
+      <c r="AB28" s="67"/>
+      <c r="AC28" s="67"/>
+      <c r="AD28" s="67"/>
+      <c r="AE28" s="67"/>
+      <c r="AF28" s="67"/>
+      <c r="AG28" s="67"/>
+      <c r="AH28" s="67"/>
+      <c r="AI28" s="67"/>
+      <c r="AJ28" s="67"/>
+      <c r="AK28" s="67"/>
+      <c r="AL28" s="67"/>
+      <c r="AM28" s="67"/>
+      <c r="AN28" s="67"/>
+      <c r="AO28" s="67"/>
+      <c r="AP28" s="67"/>
+      <c r="AQ28" s="67"/>
+      <c r="AR28" s="67"/>
+      <c r="AS28" s="67"/>
+      <c r="AT28" s="67"/>
+      <c r="AU28" s="67"/>
+      <c r="AV28" s="67"/>
+      <c r="AW28" s="67"/>
+      <c r="AX28" s="67"/>
+      <c r="AY28" s="67"/>
+      <c r="AZ28" s="67"/>
+      <c r="BA28" s="67"/>
+      <c r="BB28" s="67"/>
+      <c r="BC28" s="67"/>
     </row>
     <row r="29" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="51"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="51"/>
-      <c r="AA29" s="51"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="51"/>
-      <c r="AE29" s="51"/>
-      <c r="AF29" s="51"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="51"/>
-      <c r="AJ29" s="51"/>
-      <c r="AK29" s="51"/>
-      <c r="AL29" s="51"/>
-      <c r="AM29" s="51"/>
-      <c r="AN29" s="51"/>
-      <c r="AO29" s="51"/>
-      <c r="AP29" s="51"/>
-      <c r="AQ29" s="51"/>
-      <c r="AR29" s="51"/>
-      <c r="AS29" s="51"/>
-      <c r="AT29" s="51"/>
-      <c r="AU29" s="51"/>
-      <c r="AV29" s="51"/>
-      <c r="AW29" s="51"/>
-      <c r="AX29" s="51"/>
-      <c r="AY29" s="51"/>
-      <c r="AZ29" s="51"/>
-      <c r="BA29" s="51"/>
-      <c r="BB29" s="51"/>
-      <c r="BC29" s="51"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
+      <c r="AB29" s="67"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="67"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="67"/>
+      <c r="AK29" s="67"/>
+      <c r="AL29" s="67"/>
+      <c r="AM29" s="67"/>
+      <c r="AN29" s="67"/>
+      <c r="AO29" s="67"/>
+      <c r="AP29" s="67"/>
+      <c r="AQ29" s="67"/>
+      <c r="AR29" s="67"/>
+      <c r="AS29" s="67"/>
+      <c r="AT29" s="67"/>
+      <c r="AU29" s="67"/>
+      <c r="AV29" s="67"/>
+      <c r="AW29" s="67"/>
+      <c r="AX29" s="67"/>
+      <c r="AY29" s="67"/>
+      <c r="AZ29" s="67"/>
+      <c r="BA29" s="67"/>
+      <c r="BB29" s="67"/>
+      <c r="BC29" s="67"/>
     </row>
     <row r="30" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="51"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="51"/>
-      <c r="W30" s="51"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="Z30" s="51"/>
-      <c r="AA30" s="51"/>
-      <c r="AB30" s="51"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="51"/>
-      <c r="AE30" s="51"/>
-      <c r="AF30" s="51"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="51"/>
-      <c r="AJ30" s="51"/>
-      <c r="AK30" s="51"/>
-      <c r="AL30" s="51"/>
-      <c r="AM30" s="51"/>
-      <c r="AN30" s="51"/>
-      <c r="AO30" s="51"/>
-      <c r="AP30" s="51"/>
-      <c r="AQ30" s="51"/>
-      <c r="AR30" s="51"/>
-      <c r="AS30" s="51"/>
-      <c r="AT30" s="51"/>
-      <c r="AU30" s="51"/>
-      <c r="AV30" s="51"/>
-      <c r="AW30" s="51"/>
-      <c r="AX30" s="51"/>
-      <c r="AY30" s="51"/>
-      <c r="AZ30" s="51"/>
-      <c r="BA30" s="51"/>
-      <c r="BB30" s="51"/>
-      <c r="BC30" s="51"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="67"/>
+      <c r="AB30" s="67"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="67"/>
+      <c r="AF30" s="67"/>
+      <c r="AG30" s="67"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
+      <c r="AK30" s="67"/>
+      <c r="AL30" s="67"/>
+      <c r="AM30" s="67"/>
+      <c r="AN30" s="67"/>
+      <c r="AO30" s="67"/>
+      <c r="AP30" s="67"/>
+      <c r="AQ30" s="67"/>
+      <c r="AR30" s="67"/>
+      <c r="AS30" s="67"/>
+      <c r="AT30" s="67"/>
+      <c r="AU30" s="67"/>
+      <c r="AV30" s="67"/>
+      <c r="AW30" s="67"/>
+      <c r="AX30" s="67"/>
+      <c r="AY30" s="67"/>
+      <c r="AZ30" s="67"/>
+      <c r="BA30" s="67"/>
+      <c r="BB30" s="67"/>
+      <c r="BC30" s="67"/>
     </row>
     <row r="31" spans="1:55" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="51"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
-      <c r="Z31" s="51"/>
-      <c r="AA31" s="51"/>
-      <c r="AB31" s="51"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="51"/>
-      <c r="AE31" s="51"/>
-      <c r="AF31" s="51"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="51"/>
-      <c r="AJ31" s="51"/>
-      <c r="AK31" s="51"/>
-      <c r="AL31" s="51"/>
-      <c r="AM31" s="51"/>
-      <c r="AN31" s="51"/>
-      <c r="AO31" s="51"/>
-      <c r="AP31" s="51"/>
-      <c r="AQ31" s="51"/>
-      <c r="AR31" s="51"/>
-      <c r="AS31" s="51"/>
-      <c r="AT31" s="51"/>
-      <c r="AU31" s="51"/>
-      <c r="AV31" s="51"/>
-      <c r="AW31" s="51"/>
-      <c r="AX31" s="51"/>
-      <c r="AY31" s="51"/>
-      <c r="AZ31" s="51"/>
-      <c r="BA31" s="51"/>
-      <c r="BB31" s="51"/>
-      <c r="BC31" s="51"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+      <c r="AB31" s="67"/>
+      <c r="AC31" s="67"/>
+      <c r="AD31" s="67"/>
+      <c r="AE31" s="67"/>
+      <c r="AF31" s="67"/>
+      <c r="AG31" s="67"/>
+      <c r="AH31" s="67"/>
+      <c r="AI31" s="67"/>
+      <c r="AJ31" s="67"/>
+      <c r="AK31" s="67"/>
+      <c r="AL31" s="67"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="67"/>
+      <c r="AO31" s="67"/>
+      <c r="AP31" s="67"/>
+      <c r="AQ31" s="67"/>
+      <c r="AR31" s="67"/>
+      <c r="AS31" s="67"/>
+      <c r="AT31" s="67"/>
+      <c r="AU31" s="67"/>
+      <c r="AV31" s="67"/>
+      <c r="AW31" s="67"/>
+      <c r="AX31" s="67"/>
+      <c r="AY31" s="67"/>
+      <c r="AZ31" s="67"/>
+      <c r="BA31" s="67"/>
+      <c r="BB31" s="67"/>
+      <c r="BC31" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="A29:I31"/>
+    <mergeCell ref="J29:Q31"/>
+    <mergeCell ref="R29:U31"/>
+    <mergeCell ref="V29:AS31"/>
+    <mergeCell ref="AT29:BC31"/>
+    <mergeCell ref="A26:I28"/>
+    <mergeCell ref="J26:Q28"/>
+    <mergeCell ref="R26:U28"/>
+    <mergeCell ref="V26:AS28"/>
+    <mergeCell ref="AT26:BC28"/>
+    <mergeCell ref="A23:I25"/>
+    <mergeCell ref="J23:Q25"/>
+    <mergeCell ref="R23:U25"/>
+    <mergeCell ref="V23:AS25"/>
+    <mergeCell ref="AT23:BC25"/>
+    <mergeCell ref="A20:I22"/>
+    <mergeCell ref="J20:Q22"/>
+    <mergeCell ref="R20:U22"/>
+    <mergeCell ref="V20:AS22"/>
+    <mergeCell ref="AT20:BC22"/>
+    <mergeCell ref="A17:I19"/>
+    <mergeCell ref="J17:Q19"/>
+    <mergeCell ref="R17:U19"/>
+    <mergeCell ref="V17:AS19"/>
+    <mergeCell ref="AT17:BC19"/>
+    <mergeCell ref="A14:I16"/>
+    <mergeCell ref="J14:Q16"/>
+    <mergeCell ref="R14:U16"/>
+    <mergeCell ref="V14:AS16"/>
+    <mergeCell ref="AT14:BC16"/>
+    <mergeCell ref="A11:I13"/>
+    <mergeCell ref="J11:Q13"/>
+    <mergeCell ref="R11:U13"/>
+    <mergeCell ref="V11:AS13"/>
+    <mergeCell ref="AT11:BC13"/>
+    <mergeCell ref="A8:I10"/>
+    <mergeCell ref="J8:Q10"/>
+    <mergeCell ref="R8:U10"/>
+    <mergeCell ref="V8:AS10"/>
+    <mergeCell ref="AT8:BC10"/>
+    <mergeCell ref="A5:I7"/>
+    <mergeCell ref="J5:Q7"/>
+    <mergeCell ref="R5:U7"/>
+    <mergeCell ref="V5:AS7"/>
+    <mergeCell ref="AT5:BC7"/>
     <mergeCell ref="AT1:AX1"/>
     <mergeCell ref="AY1:BC1"/>
     <mergeCell ref="A2:I3"/>
@@ -15291,51 +15089,6 @@
     <mergeCell ref="R1:AI1"/>
     <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="AO1:AS1"/>
-    <mergeCell ref="A5:I7"/>
-    <mergeCell ref="J5:Q7"/>
-    <mergeCell ref="R5:U7"/>
-    <mergeCell ref="V5:AS7"/>
-    <mergeCell ref="AT5:BC7"/>
-    <mergeCell ref="A8:I10"/>
-    <mergeCell ref="J8:Q10"/>
-    <mergeCell ref="R8:U10"/>
-    <mergeCell ref="V8:AS10"/>
-    <mergeCell ref="AT8:BC10"/>
-    <mergeCell ref="A11:I13"/>
-    <mergeCell ref="J11:Q13"/>
-    <mergeCell ref="R11:U13"/>
-    <mergeCell ref="V11:AS13"/>
-    <mergeCell ref="AT11:BC13"/>
-    <mergeCell ref="A14:I16"/>
-    <mergeCell ref="J14:Q16"/>
-    <mergeCell ref="R14:U16"/>
-    <mergeCell ref="V14:AS16"/>
-    <mergeCell ref="AT14:BC16"/>
-    <mergeCell ref="A17:I19"/>
-    <mergeCell ref="J17:Q19"/>
-    <mergeCell ref="R17:U19"/>
-    <mergeCell ref="V17:AS19"/>
-    <mergeCell ref="AT17:BC19"/>
-    <mergeCell ref="A20:I22"/>
-    <mergeCell ref="J20:Q22"/>
-    <mergeCell ref="R20:U22"/>
-    <mergeCell ref="V20:AS22"/>
-    <mergeCell ref="AT20:BC22"/>
-    <mergeCell ref="A23:I25"/>
-    <mergeCell ref="J23:Q25"/>
-    <mergeCell ref="R23:U25"/>
-    <mergeCell ref="V23:AS25"/>
-    <mergeCell ref="AT23:BC25"/>
-    <mergeCell ref="A26:I28"/>
-    <mergeCell ref="J26:Q28"/>
-    <mergeCell ref="R26:U28"/>
-    <mergeCell ref="V26:AS28"/>
-    <mergeCell ref="AT26:BC28"/>
-    <mergeCell ref="A29:I31"/>
-    <mergeCell ref="J29:Q31"/>
-    <mergeCell ref="R29:U31"/>
-    <mergeCell ref="V29:AS31"/>
-    <mergeCell ref="AT29:BC31"/>
   </mergeCells>
   <phoneticPr fontId="32"/>
   <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="1.0291666666666699" bottom="1.07083333333333" header="0.31527777777777799" footer="0.31527777777777799"/>
@@ -15350,7 +15103,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
@@ -15358,31 +15111,41 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A60" t="s">
-        <v>20</v>
-      </c>
-      <c r="L60" s="26" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="26" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -15409,12 +15172,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -15440,137 +15203,137 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B41" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B60" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B81" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M81" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B99" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B100" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M100" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B118" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B119" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M119" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B137" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B138" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M138" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B157" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B158" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M158" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" spans="2:2" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B176" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="177" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B177" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M177" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" spans="2:13" ht="18.75" x14ac:dyDescent="0.15">
       <c r="B195" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="196" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B196" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M196" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -15599,28 +15362,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A27" s="27" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -15645,15 +15408,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
@@ -15661,15 +15424,15 @@
     </row>
     <row r="21" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A21" s="27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
@@ -15719,12 +15482,12 @@
     </row>
     <row r="38" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A38" s="27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A39" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
@@ -15732,15 +15495,15 @@
     </row>
     <row r="41" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A41" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
@@ -15784,67 +15547,67 @@
     </row>
     <row r="57" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A57" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I58" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A72" s="27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I73" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A87" s="27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I88" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A102" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I103" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A117" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I118" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -15873,15 +15636,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -15928,15 +15691,15 @@
     </row>
     <row r="17" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A17" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
@@ -15983,15 +15746,15 @@
     </row>
     <row r="33" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A33" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
